--- a/Plannification/Fiche_recette_LaDiscorde.xlsx
+++ b/Plannification/Fiche_recette_LaDiscorde.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://stfelixlasalle-my.sharepoint.com/personal/julian_chedotal_stfelixlasalle_fr/Documents/Documents/GitHub/mini_projet2/Plannification/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F1740F19-708E-41C2-97B7-09A7E76525B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="27" documentId="8_{F1740F19-708E-41C2-97B7-09A7E76525B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A92C5440-D309-4411-B32C-D698045EF374}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F0C29018-6AE5-422C-A279-19C0BD496EEE}"/>
   </bookViews>
@@ -36,10 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="42">
-  <si>
-    <t>Julian Chedotal / Tristan Bonnard</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="50">
   <si>
     <t>Fiche recettes</t>
   </si>
@@ -182,6 +179,33 @@
   </si>
   <si>
     <t xml:space="preserve"> 1/x</t>
+  </si>
+  <si>
+    <t>Scénario 3.</t>
+  </si>
+  <si>
+    <t>Connexion à la page web</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Avoir lancé la BDD / Avoir lancé le serveur </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 3/x</t>
+  </si>
+  <si>
+    <t>Laner un navigateur web</t>
+  </si>
+  <si>
+    <t>Le navigateur ce lance</t>
+  </si>
+  <si>
+    <t>Cliquer sur la barre de navigation du navigateur et entrer l'hostname du serveur</t>
+  </si>
+  <si>
+    <t>C206-03:3000/login.html</t>
+  </si>
+  <si>
+    <t>vous arrivez sur le menu de connexion de LaDiscorde</t>
   </si>
 </sst>
 </file>
@@ -431,193 +455,208 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="69">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -954,604 +993,867 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E692836E-065C-4DA9-AE7D-E8BAD5876E51}">
-  <dimension ref="A1:H49"/>
+  <dimension ref="A1:H73"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24.7109375" customWidth="1"/>
     <col min="2" max="2" width="29.5703125" customWidth="1"/>
     <col min="3" max="3" width="19.85546875" customWidth="1"/>
+    <col min="4" max="4" width="17" customWidth="1"/>
     <col min="5" max="5" width="28" customWidth="1"/>
     <col min="6" max="6" width="27" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1" s="62" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="62"/>
+      <c r="E1" s="62"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="2"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+    </row>
+    <row r="3" spans="1:7" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A3" s="2"/>
+      <c r="B3" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="43" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C1" s="2" t="s">
+      <c r="D3" s="43"/>
+      <c r="E3" s="43"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="2"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="2"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="2"/>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="2"/>
+      <c r="B7" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="C7" s="44" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" s="44"/>
+      <c r="E7" s="44"/>
+      <c r="F7" s="45"/>
+      <c r="G7" s="2"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="2"/>
+      <c r="B8" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C8" s="63" t="s">
+        <v>26</v>
+      </c>
+      <c r="D8" s="63"/>
+      <c r="E8" s="63"/>
+      <c r="F8" s="63"/>
+      <c r="G8" s="2"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="2"/>
+      <c r="B9" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C9" s="63"/>
+      <c r="D9" s="63"/>
+      <c r="E9" s="63"/>
+      <c r="F9" s="63"/>
+      <c r="G9" s="2"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="2"/>
+      <c r="B10" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C10" s="63" t="s">
+        <v>27</v>
+      </c>
+      <c r="D10" s="63"/>
+      <c r="E10" s="63"/>
+      <c r="F10" s="63"/>
+      <c r="G10" s="2"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="2"/>
+      <c r="B11" s="56" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="57"/>
+      <c r="D11" s="57"/>
+      <c r="E11" s="57"/>
+      <c r="F11" s="58"/>
+      <c r="G11" s="2"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="2"/>
+      <c r="B12" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="D12" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="E12" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="F12" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G12" s="2"/>
+    </row>
+    <row r="13" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A13" s="2"/>
+      <c r="B13" s="5">
         <v>1</v>
       </c>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="3"/>
-      <c r="B2" s="4"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-    </row>
-    <row r="3" spans="1:7" ht="26.25" x14ac:dyDescent="0.25">
-      <c r="A3" s="3"/>
-      <c r="B3" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="3"/>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="3"/>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="3"/>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="3"/>
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="3"/>
-      <c r="B7" s="39" t="s">
-        <v>3</v>
-      </c>
-      <c r="C7" s="40" t="s">
-        <v>4</v>
-      </c>
-      <c r="D7" s="40"/>
-      <c r="E7" s="40"/>
-      <c r="F7" s="41"/>
-      <c r="G7" s="3"/>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="3"/>
-      <c r="B8" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="D8" s="8"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="8"/>
-      <c r="G8" s="3"/>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="3"/>
-      <c r="B9" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="C9" s="8"/>
-      <c r="D9" s="8"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="8"/>
-      <c r="G9" s="3"/>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="3"/>
-      <c r="B10" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="C10" s="8" t="s">
+      <c r="C13" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="3"/>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="3"/>
-      <c r="B11" s="42" t="s">
-        <v>8</v>
-      </c>
-      <c r="C11" s="43"/>
-      <c r="D11" s="43"/>
-      <c r="E11" s="43"/>
-      <c r="F11" s="44"/>
-      <c r="G11" s="3"/>
-    </row>
-    <row r="12" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A12" s="3"/>
-      <c r="B12" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="45" t="s">
-        <v>10</v>
-      </c>
-      <c r="D12" s="45" t="s">
-        <v>11</v>
-      </c>
-      <c r="E12" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="F12" s="47" t="s">
+      <c r="D13" s="5"/>
+      <c r="E13" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="F13" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="G12" s="3"/>
-    </row>
-    <row r="13" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A13" s="3"/>
-      <c r="B13" s="7">
-        <v>1</v>
-      </c>
-      <c r="C13" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="D13" s="7"/>
-      <c r="E13" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="F13" s="7" t="s">
+      <c r="G13" s="2"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="2"/>
+      <c r="B14" s="47"/>
+      <c r="C14" s="48"/>
+      <c r="D14" s="48"/>
+      <c r="E14" s="48"/>
+      <c r="F14" s="49"/>
+      <c r="G14" s="2"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="2"/>
+      <c r="B15" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="G13" s="3"/>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="3"/>
-      <c r="B14" s="53"/>
-      <c r="C14" s="54"/>
-      <c r="D14" s="54"/>
-      <c r="E14" s="54"/>
-      <c r="F14" s="55"/>
-      <c r="G14" s="3"/>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="3"/>
-      <c r="B15" s="48" t="s">
+      <c r="C15" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="C15" s="51" t="s">
+      <c r="D15" s="19"/>
+      <c r="E15" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="D15" s="52"/>
-      <c r="E15" s="51" t="s">
+      <c r="F15" s="19"/>
+      <c r="G15" s="2"/>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="2"/>
+      <c r="B16" s="53" t="s">
         <v>17</v>
       </c>
-      <c r="F15" s="52"/>
-      <c r="G15" s="3"/>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="3"/>
-      <c r="B16" s="13" t="s">
+      <c r="C16" s="54"/>
+      <c r="D16" s="54"/>
+      <c r="E16" s="54"/>
+      <c r="F16" s="55"/>
+      <c r="G16" s="2"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" s="2"/>
+      <c r="B17" s="50" t="s">
         <v>18</v>
       </c>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="15"/>
-      <c r="G16" s="3"/>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" s="3"/>
-      <c r="B17" s="56" t="s">
+      <c r="C17" s="51"/>
+      <c r="D17" s="51"/>
+      <c r="E17" s="51"/>
+      <c r="F17" s="52"/>
+      <c r="G17" s="2"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" s="2"/>
+      <c r="B18" s="32" t="s">
         <v>19</v>
       </c>
-      <c r="C17" s="57"/>
-      <c r="D17" s="57"/>
-      <c r="E17" s="57"/>
-      <c r="F17" s="58"/>
-      <c r="G17" s="3"/>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="3"/>
-      <c r="B18" s="19" t="s">
+      <c r="C18" s="33"/>
+      <c r="D18" s="33"/>
+      <c r="E18" s="33"/>
+      <c r="F18" s="34"/>
+      <c r="G18" s="2"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" s="2"/>
+      <c r="B19" s="35" t="s">
         <v>20</v>
       </c>
-      <c r="C18" s="59"/>
-      <c r="D18" s="59"/>
-      <c r="E18" s="59"/>
-      <c r="F18" s="20"/>
-      <c r="G18" s="3"/>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="3"/>
-      <c r="B19" s="21" t="s">
+      <c r="C19" s="36"/>
+      <c r="D19" s="36"/>
+      <c r="E19" s="36"/>
+      <c r="F19" s="37"/>
+      <c r="G19" s="2"/>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" s="2"/>
+      <c r="B20" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="C19" s="22"/>
-      <c r="D19" s="22"/>
-      <c r="E19" s="22"/>
-      <c r="F19" s="23"/>
-      <c r="G19" s="3"/>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="3"/>
-      <c r="B20" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="C20" s="31"/>
-      <c r="D20" s="31"/>
-      <c r="E20" s="31"/>
-      <c r="F20" s="32"/>
-      <c r="G20" s="3"/>
+      <c r="C20" s="21"/>
+      <c r="D20" s="21"/>
+      <c r="E20" s="21"/>
+      <c r="F20" s="22"/>
+      <c r="G20" s="2"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="3"/>
-      <c r="B21" s="33"/>
-      <c r="C21" s="60"/>
-      <c r="D21" s="60"/>
-      <c r="E21" s="60"/>
-      <c r="F21" s="34"/>
-      <c r="G21" s="3"/>
+      <c r="A21" s="2"/>
+      <c r="B21" s="23"/>
+      <c r="C21" s="24"/>
+      <c r="D21" s="24"/>
+      <c r="E21" s="24"/>
+      <c r="F21" s="25"/>
+      <c r="G21" s="2"/>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="3"/>
-      <c r="B22" s="35"/>
-      <c r="C22" s="36"/>
-      <c r="D22" s="36"/>
-      <c r="E22" s="36"/>
-      <c r="F22" s="37"/>
-      <c r="G22" s="3"/>
+      <c r="A22" s="2"/>
+      <c r="B22" s="26"/>
+      <c r="C22" s="27"/>
+      <c r="D22" s="27"/>
+      <c r="E22" s="27"/>
+      <c r="F22" s="28"/>
+      <c r="G22" s="2"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="3"/>
-      <c r="G23" s="3"/>
+      <c r="A23" s="2"/>
+      <c r="G23" s="2"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="25" t="s">
-        <v>41</v>
-      </c>
-      <c r="B24" s="26"/>
-      <c r="C24" s="26"/>
-      <c r="D24" s="26"/>
-      <c r="E24" s="26"/>
-      <c r="F24" s="26"/>
-      <c r="G24" s="26"/>
+      <c r="A24" s="41" t="s">
+        <v>40</v>
+      </c>
+      <c r="B24" s="42"/>
+      <c r="C24" s="42"/>
+      <c r="D24" s="42"/>
+      <c r="E24" s="42"/>
+      <c r="F24" s="42"/>
+      <c r="G24" s="42"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="25"/>
-      <c r="B26" s="26"/>
-      <c r="C26" s="26"/>
-      <c r="D26" s="26"/>
-      <c r="E26" s="26"/>
-      <c r="F26" s="26"/>
-      <c r="G26" s="26"/>
+      <c r="A26" s="41"/>
+      <c r="B26" s="42"/>
+      <c r="C26" s="42"/>
+      <c r="D26" s="42"/>
+      <c r="E26" s="42"/>
+      <c r="F26" s="42"/>
+      <c r="G26" s="42"/>
     </row>
     <row r="27" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B27" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C27" s="43" t="s">
+        <v>31</v>
+      </c>
+      <c r="D27" s="43"/>
+      <c r="E27" s="43"/>
+      <c r="F27" s="43"/>
+      <c r="G27" s="2"/>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" s="2"/>
+      <c r="B28" s="2"/>
+      <c r="C28" s="2"/>
+      <c r="D28" s="2"/>
+      <c r="E28" s="2"/>
+      <c r="F28" s="2"/>
+      <c r="G28" s="2"/>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" s="2"/>
+      <c r="B29" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="C29" s="44" t="s">
         <v>23</v>
       </c>
-      <c r="C27" s="6" t="s">
+      <c r="D29" s="44"/>
+      <c r="E29" s="44"/>
+      <c r="F29" s="45"/>
+      <c r="G29" s="2"/>
+      <c r="H29" s="17"/>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" s="2"/>
+      <c r="B30" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C30" s="46" t="s">
+        <v>31</v>
+      </c>
+      <c r="D30" s="46"/>
+      <c r="E30" s="46"/>
+      <c r="F30" s="46"/>
+      <c r="G30" s="2"/>
+      <c r="H30" s="17"/>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" s="2"/>
+      <c r="B31" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C31" s="46"/>
+      <c r="D31" s="46"/>
+      <c r="E31" s="46"/>
+      <c r="F31" s="46"/>
+      <c r="G31" s="2"/>
+      <c r="H31" s="17"/>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" s="2"/>
+      <c r="B32" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C32" s="46" t="s">
         <v>32</v>
       </c>
-      <c r="D27" s="6"/>
-      <c r="E27" s="6"/>
-      <c r="F27" s="6"/>
-      <c r="G27" s="3"/>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" s="3"/>
-      <c r="B28" s="3"/>
-      <c r="C28" s="3"/>
-      <c r="D28" s="3"/>
-      <c r="E28" s="3"/>
-      <c r="F28" s="3"/>
-      <c r="G28" s="3"/>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" s="3"/>
-      <c r="B29" s="39" t="s">
+      <c r="D32" s="46"/>
+      <c r="E32" s="46"/>
+      <c r="F32" s="46"/>
+      <c r="G32" s="2"/>
+      <c r="H32" s="17"/>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" s="2"/>
+      <c r="B33" s="56" t="s">
+        <v>7</v>
+      </c>
+      <c r="C33" s="57"/>
+      <c r="D33" s="57"/>
+      <c r="E33" s="57"/>
+      <c r="F33" s="58"/>
+      <c r="G33" s="2"/>
+      <c r="H33" s="17"/>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" s="2"/>
+      <c r="B34" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="C34" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="D34" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="E34" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="F34" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G34" s="2"/>
+      <c r="H34" s="17"/>
+    </row>
+    <row r="35" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A35" s="2"/>
+      <c r="B35" s="5">
+        <v>1</v>
+      </c>
+      <c r="C35" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="D35" s="5"/>
+      <c r="E35" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="F35" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G35" s="2"/>
+      <c r="H35" s="17"/>
+    </row>
+    <row r="36" spans="1:8" ht="60" x14ac:dyDescent="0.25">
+      <c r="A36" s="2"/>
+      <c r="B36" s="8">
+        <v>2</v>
+      </c>
+      <c r="C36" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="D36" s="8"/>
+      <c r="E36" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="F36" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G36" s="2"/>
+      <c r="H36" s="17"/>
+    </row>
+    <row r="37" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+      <c r="A37" s="2"/>
+      <c r="B37" s="7">
         <v>3</v>
       </c>
-      <c r="C29" s="40" t="s">
-        <v>24</v>
-      </c>
-      <c r="D29" s="40"/>
-      <c r="E29" s="40"/>
-      <c r="F29" s="41"/>
-      <c r="G29" s="3"/>
-      <c r="H29" s="50"/>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="3"/>
-      <c r="B30" s="7" t="s">
+      <c r="C37" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="D37" s="7"/>
+      <c r="E37" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="F37" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G37" s="2"/>
+      <c r="H37" s="17"/>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" s="2"/>
+      <c r="B38" s="59"/>
+      <c r="C38" s="60"/>
+      <c r="D38" s="60"/>
+      <c r="E38" s="60"/>
+      <c r="F38" s="61"/>
+      <c r="G38" s="2"/>
+      <c r="H38" s="17"/>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" s="2"/>
+      <c r="B39" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="C39" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="D39" s="14"/>
+      <c r="E39" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="F39" s="14"/>
+      <c r="G39" s="2"/>
+      <c r="H39" s="17"/>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" s="2"/>
+      <c r="B40" s="38" t="s">
+        <v>17</v>
+      </c>
+      <c r="C40" s="39"/>
+      <c r="D40" s="39"/>
+      <c r="E40" s="39"/>
+      <c r="F40" s="40"/>
+      <c r="G40" s="2"/>
+      <c r="H40" s="17"/>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" s="2"/>
+      <c r="B41" s="29" t="s">
+        <v>18</v>
+      </c>
+      <c r="C41" s="30"/>
+      <c r="D41" s="30"/>
+      <c r="E41" s="30"/>
+      <c r="F41" s="31"/>
+      <c r="G41" s="2"/>
+      <c r="H41" s="17"/>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" s="2"/>
+      <c r="B42" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="C42" s="33"/>
+      <c r="D42" s="33"/>
+      <c r="E42" s="33"/>
+      <c r="F42" s="34"/>
+      <c r="G42" s="2"/>
+      <c r="H42" s="17"/>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" s="2"/>
+      <c r="B43" s="35" t="s">
+        <v>20</v>
+      </c>
+      <c r="C43" s="36"/>
+      <c r="D43" s="36"/>
+      <c r="E43" s="36"/>
+      <c r="F43" s="37"/>
+      <c r="G43" s="2"/>
+      <c r="H43" s="17"/>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" s="2"/>
+      <c r="B44" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="C44" s="21"/>
+      <c r="D44" s="21"/>
+      <c r="E44" s="21"/>
+      <c r="F44" s="22"/>
+      <c r="G44" s="2"/>
+      <c r="H44" s="17"/>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" s="2"/>
+      <c r="B45" s="23"/>
+      <c r="C45" s="24"/>
+      <c r="D45" s="24"/>
+      <c r="E45" s="24"/>
+      <c r="F45" s="25"/>
+      <c r="G45" s="2"/>
+      <c r="H45" s="17"/>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" s="2"/>
+      <c r="B46" s="26"/>
+      <c r="C46" s="27"/>
+      <c r="D46" s="27"/>
+      <c r="E46" s="27"/>
+      <c r="F46" s="28"/>
+      <c r="G46" s="2"/>
+      <c r="H46" s="17"/>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H47" s="17"/>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" s="2"/>
+      <c r="B48" s="2"/>
+      <c r="C48" s="2"/>
+      <c r="D48" s="2"/>
+      <c r="E48" s="2"/>
+      <c r="F48" s="2"/>
+      <c r="G48" s="2"/>
+      <c r="H48" s="17"/>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A49" s="41" t="s">
+        <v>39</v>
+      </c>
+      <c r="B49" s="42"/>
+      <c r="C49" s="42"/>
+      <c r="D49" s="42"/>
+      <c r="E49" s="42"/>
+      <c r="F49" s="42"/>
+      <c r="G49" s="42"/>
+    </row>
+    <row r="52" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A52" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C52" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="D52" s="43"/>
+      <c r="E52" s="43"/>
+      <c r="F52" s="43"/>
+      <c r="G52" s="2"/>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A53" s="2"/>
+      <c r="B53" s="2"/>
+      <c r="C53" s="2"/>
+      <c r="D53" s="2"/>
+      <c r="E53" s="2"/>
+      <c r="F53" s="2"/>
+      <c r="G53" s="2"/>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A54" s="2"/>
+      <c r="B54" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="C54" s="44" t="s">
+        <v>23</v>
+      </c>
+      <c r="D54" s="44"/>
+      <c r="E54" s="44"/>
+      <c r="F54" s="45"/>
+      <c r="G54" s="2"/>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A55" s="2"/>
+      <c r="B55" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C55" s="46" t="s">
+        <v>31</v>
+      </c>
+      <c r="D55" s="46"/>
+      <c r="E55" s="46"/>
+      <c r="F55" s="46"/>
+      <c r="G55" s="2"/>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A56" s="2"/>
+      <c r="B56" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="C30" s="27" t="s">
-        <v>32</v>
-      </c>
-      <c r="D30" s="27"/>
-      <c r="E30" s="27"/>
-      <c r="F30" s="27"/>
-      <c r="G30" s="3"/>
-      <c r="H30" s="50"/>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A31" s="3"/>
-      <c r="B31" s="9" t="s">
+      <c r="C56" s="46"/>
+      <c r="D56" s="46"/>
+      <c r="E56" s="46"/>
+      <c r="F56" s="46"/>
+      <c r="G56" s="2"/>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A57" s="2"/>
+      <c r="B57" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C31" s="27"/>
-      <c r="D31" s="27"/>
-      <c r="E31" s="27"/>
-      <c r="F31" s="27"/>
-      <c r="G31" s="3"/>
-      <c r="H31" s="50"/>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" s="3"/>
-      <c r="B32" s="9" t="s">
+      <c r="C57" s="46" t="s">
+        <v>43</v>
+      </c>
+      <c r="D57" s="46"/>
+      <c r="E57" s="46"/>
+      <c r="F57" s="46"/>
+      <c r="G57" s="2"/>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A58" s="2"/>
+      <c r="B58" s="56" t="s">
         <v>7</v>
       </c>
-      <c r="C32" s="27" t="s">
-        <v>33</v>
-      </c>
-      <c r="D32" s="27"/>
-      <c r="E32" s="27"/>
-      <c r="F32" s="27"/>
-      <c r="G32" s="3"/>
-      <c r="H32" s="50"/>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A33" s="3"/>
-      <c r="B33" s="42" t="s">
+      <c r="C58" s="57"/>
+      <c r="D58" s="57"/>
+      <c r="E58" s="57"/>
+      <c r="F58" s="58"/>
+      <c r="G58" s="2"/>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A59" s="2"/>
+      <c r="B59" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="C33" s="43"/>
-      <c r="D33" s="43"/>
-      <c r="E33" s="43"/>
-      <c r="F33" s="44"/>
-      <c r="G33" s="3"/>
-      <c r="H33" s="50"/>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A34" s="3"/>
-      <c r="B34" s="45" t="s">
+      <c r="C59" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="C34" s="45" t="s">
+      <c r="D59" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="D34" s="45" t="s">
+      <c r="E59" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="E34" s="46" t="s">
+      <c r="F59" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="F34" s="47" t="s">
+      <c r="G59" s="2"/>
+    </row>
+    <row r="60" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A60" s="2"/>
+      <c r="B60" s="5">
+        <v>1</v>
+      </c>
+      <c r="C60" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="D60" s="5"/>
+      <c r="E60" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="F60" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="G34" s="3"/>
-      <c r="H34" s="50"/>
-    </row>
-    <row r="35" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A35" s="3"/>
-      <c r="B35" s="7">
-        <v>1</v>
-      </c>
-      <c r="C35" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="D35" s="7"/>
-      <c r="E35" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="F35" s="7" t="s">
+      <c r="G60" s="2"/>
+    </row>
+    <row r="61" spans="1:7" ht="75" x14ac:dyDescent="0.25">
+      <c r="A61" s="2"/>
+      <c r="B61" s="8">
+        <v>2</v>
+      </c>
+      <c r="C61" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="D61" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="E61" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="F61" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G61" s="2"/>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A62" s="2"/>
+      <c r="B62" s="66"/>
+      <c r="C62" s="67"/>
+      <c r="D62" s="67"/>
+      <c r="E62" s="67"/>
+      <c r="F62" s="68"/>
+      <c r="G62" s="2"/>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A63" s="2"/>
+      <c r="B63" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="G35" s="3"/>
-      <c r="H35" s="50"/>
-    </row>
-    <row r="36" spans="1:8" ht="60" x14ac:dyDescent="0.25">
-      <c r="A36" s="3"/>
-      <c r="B36" s="11">
-        <v>2</v>
-      </c>
-      <c r="C36" s="12" t="s">
-        <v>36</v>
-      </c>
-      <c r="D36" s="11"/>
-      <c r="E36" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="F36" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="G36" s="3"/>
-      <c r="H36" s="50"/>
-    </row>
-    <row r="37" spans="1:8" ht="45" x14ac:dyDescent="0.25">
-      <c r="A37" s="3"/>
-      <c r="B37" s="10">
-        <v>3</v>
-      </c>
-      <c r="C37" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="D37" s="10"/>
-      <c r="E37" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="F37" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="G37" s="3"/>
-      <c r="H37" s="50"/>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A38" s="3"/>
-      <c r="B38" s="61"/>
-      <c r="C38" s="62"/>
-      <c r="D38" s="62"/>
-      <c r="E38" s="62"/>
-      <c r="F38" s="63"/>
-      <c r="G38" s="3"/>
-      <c r="H38" s="50"/>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A39" s="3"/>
-      <c r="B39" s="48" t="s">
+      <c r="C63" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="C39" s="49" t="s">
+      <c r="D63" s="19"/>
+      <c r="E63" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="D39" s="47"/>
-      <c r="E39" s="49" t="s">
+      <c r="F63" s="19"/>
+      <c r="G63" s="2"/>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A64" s="2"/>
+      <c r="B64" s="38" t="s">
         <v>17</v>
       </c>
-      <c r="F39" s="47"/>
-      <c r="G39" s="3"/>
-      <c r="H39" s="50"/>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A40" s="3"/>
-      <c r="B40" s="28" t="s">
+      <c r="C64" s="39"/>
+      <c r="D64" s="39"/>
+      <c r="E64" s="39"/>
+      <c r="F64" s="40"/>
+      <c r="G64" s="2"/>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A65" s="2"/>
+      <c r="B65" s="29" t="s">
         <v>18</v>
       </c>
-      <c r="C40" s="29"/>
-      <c r="D40" s="29"/>
-      <c r="E40" s="29"/>
-      <c r="F40" s="30"/>
-      <c r="G40" s="3"/>
-      <c r="H40" s="50"/>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A41" s="3"/>
-      <c r="B41" s="16" t="s">
+      <c r="C65" s="30"/>
+      <c r="D65" s="30"/>
+      <c r="E65" s="30"/>
+      <c r="F65" s="31"/>
+      <c r="G65" s="2"/>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A66" s="2"/>
+      <c r="B66" s="32" t="s">
         <v>19</v>
       </c>
-      <c r="C41" s="17"/>
-      <c r="D41" s="17"/>
-      <c r="E41" s="17"/>
-      <c r="F41" s="18"/>
-      <c r="G41" s="3"/>
-      <c r="H41" s="50"/>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A42" s="3"/>
-      <c r="B42" s="19" t="s">
+      <c r="C66" s="65"/>
+      <c r="D66" s="65"/>
+      <c r="E66" s="65"/>
+      <c r="F66" s="34"/>
+      <c r="G66" s="2"/>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A67" s="2"/>
+      <c r="B67" s="35" t="s">
         <v>20</v>
       </c>
-      <c r="C42" s="59"/>
-      <c r="D42" s="59"/>
-      <c r="E42" s="59"/>
-      <c r="F42" s="20"/>
-      <c r="G42" s="3"/>
-      <c r="H42" s="50"/>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A43" s="3"/>
-      <c r="B43" s="21" t="s">
+      <c r="C67" s="36"/>
+      <c r="D67" s="36"/>
+      <c r="E67" s="36"/>
+      <c r="F67" s="37"/>
+      <c r="G67" s="2"/>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A68" s="2"/>
+      <c r="B68" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="C43" s="22"/>
-      <c r="D43" s="22"/>
-      <c r="E43" s="22"/>
-      <c r="F43" s="23"/>
-      <c r="G43" s="3"/>
-      <c r="H43" s="50"/>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A44" s="3"/>
-      <c r="B44" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="C44" s="31"/>
-      <c r="D44" s="31"/>
-      <c r="E44" s="31"/>
-      <c r="F44" s="32"/>
-      <c r="G44" s="3"/>
-      <c r="H44" s="50"/>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A45" s="3"/>
-      <c r="B45" s="33"/>
-      <c r="C45" s="60"/>
-      <c r="D45" s="60"/>
-      <c r="E45" s="60"/>
-      <c r="F45" s="34"/>
-      <c r="G45" s="3"/>
-      <c r="H45" s="50"/>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A46" s="3"/>
-      <c r="B46" s="35"/>
-      <c r="C46" s="36"/>
-      <c r="D46" s="36"/>
-      <c r="E46" s="36"/>
-      <c r="F46" s="37"/>
-      <c r="G46" s="3"/>
-      <c r="H46" s="50"/>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="H47" s="50"/>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A48" s="3"/>
-      <c r="B48" s="3"/>
-      <c r="C48" s="3"/>
-      <c r="D48" s="3"/>
-      <c r="E48" s="3"/>
-      <c r="F48" s="3"/>
-      <c r="G48" s="3"/>
-      <c r="H48" s="50"/>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A49" s="25" t="s">
-        <v>40</v>
-      </c>
-      <c r="B49" s="26"/>
-      <c r="C49" s="26"/>
-      <c r="D49" s="26"/>
-      <c r="E49" s="26"/>
-      <c r="F49" s="26"/>
-      <c r="G49" s="26"/>
+      <c r="C68" s="21"/>
+      <c r="D68" s="21"/>
+      <c r="E68" s="21"/>
+      <c r="F68" s="22"/>
+      <c r="G68" s="2"/>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A69" s="2"/>
+      <c r="B69" s="23"/>
+      <c r="C69" s="64"/>
+      <c r="D69" s="64"/>
+      <c r="E69" s="64"/>
+      <c r="F69" s="25"/>
+      <c r="G69" s="2"/>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A70" s="2"/>
+      <c r="B70" s="26"/>
+      <c r="C70" s="27"/>
+      <c r="D70" s="27"/>
+      <c r="E70" s="27"/>
+      <c r="F70" s="28"/>
+      <c r="G70" s="2"/>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A71" s="2"/>
+      <c r="G71" s="2"/>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A73" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="B73" s="42"/>
+      <c r="C73" s="42"/>
+      <c r="D73" s="42"/>
+      <c r="E73" s="42"/>
+      <c r="F73" s="42"/>
+      <c r="G73" s="42"/>
     </row>
   </sheetData>
-  <mergeCells count="28">
-    <mergeCell ref="B44:F46"/>
-    <mergeCell ref="B41:F41"/>
-    <mergeCell ref="B42:F42"/>
-    <mergeCell ref="B43:F43"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="A24:G24"/>
-    <mergeCell ref="C27:F27"/>
-    <mergeCell ref="C29:F29"/>
-    <mergeCell ref="C30:F30"/>
-    <mergeCell ref="C31:F31"/>
+  <mergeCells count="41">
+    <mergeCell ref="B65:F65"/>
+    <mergeCell ref="B66:F66"/>
+    <mergeCell ref="B67:F67"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B62:F62"/>
+    <mergeCell ref="A73:G73"/>
+    <mergeCell ref="B68:F70"/>
+    <mergeCell ref="B58:F58"/>
+    <mergeCell ref="C52:F52"/>
+    <mergeCell ref="C54:F54"/>
+    <mergeCell ref="C55:F55"/>
+    <mergeCell ref="C56:F56"/>
+    <mergeCell ref="C57:F57"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="C3:E3"/>
+    <mergeCell ref="C7:F7"/>
+    <mergeCell ref="C8:F8"/>
+    <mergeCell ref="C9:F9"/>
+    <mergeCell ref="C10:F10"/>
     <mergeCell ref="C32:F32"/>
     <mergeCell ref="A49:G49"/>
     <mergeCell ref="B14:F14"/>
@@ -1563,13 +1865,16 @@
     <mergeCell ref="B33:F33"/>
     <mergeCell ref="B38:F38"/>
     <mergeCell ref="A26:G26"/>
-    <mergeCell ref="B11:F11"/>
-    <mergeCell ref="C1:E1"/>
-    <mergeCell ref="C3:E3"/>
-    <mergeCell ref="C7:F7"/>
-    <mergeCell ref="C8:F8"/>
-    <mergeCell ref="C9:F9"/>
-    <mergeCell ref="C10:F10"/>
+    <mergeCell ref="A24:G24"/>
+    <mergeCell ref="C27:F27"/>
+    <mergeCell ref="C29:F29"/>
+    <mergeCell ref="C30:F30"/>
+    <mergeCell ref="C31:F31"/>
+    <mergeCell ref="B44:F46"/>
+    <mergeCell ref="B41:F41"/>
+    <mergeCell ref="B42:F42"/>
+    <mergeCell ref="B43:F43"/>
+    <mergeCell ref="B40:F40"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Plannification/Fiche_recette_LaDiscorde.xlsx
+++ b/Plannification/Fiche_recette_LaDiscorde.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://stfelixlasalle-my.sharepoint.com/personal/julian_chedotal_stfelixlasalle_fr/Documents/Documents/GitHub/mini_projet2/Plannification/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\matisse.begaud\Documents\GitHub\mini_projet2\Plannification\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="27" documentId="8_{F1740F19-708E-41C2-97B7-09A7E76525B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A92C5440-D309-4411-B32C-D698045EF374}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{515302C5-FDF2-4EA1-9EDD-8EE568592BD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F0C29018-6AE5-422C-A279-19C0BD496EEE}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="85">
   <si>
     <t>Fiche recettes</t>
   </si>
@@ -206,6 +206,111 @@
   </si>
   <si>
     <t>vous arrivez sur le menu de connexion de LaDiscorde</t>
+  </si>
+  <si>
+    <t>Scénario 4.</t>
+  </si>
+  <si>
+    <t>Avoir lancé la BDD / Avoir lancé le serveur / être connecter a la page</t>
+  </si>
+  <si>
+    <t>redirection vers http://C206-03:3000/login.html</t>
+  </si>
+  <si>
+    <t>Scénario 5.</t>
+  </si>
+  <si>
+    <t>Vérification de mail</t>
+  </si>
+  <si>
+    <t>Entrer dans votre messagerie email</t>
+  </si>
+  <si>
+    <t>Avoir accès a ses email</t>
+  </si>
+  <si>
+    <t>Cliquer sur le mail se nommant "Vérifie ton adresse email — LaDiscorde"</t>
+  </si>
+  <si>
+    <t>Cliquer sur le bouton "Vérifier mon email"</t>
+  </si>
+  <si>
+    <t>Entrer dans le mail, comportant un bouton "Vérifier mon email"</t>
+  </si>
+  <si>
+    <t>Scénario 6.</t>
+  </si>
+  <si>
+    <t>Connexion au compte</t>
+  </si>
+  <si>
+    <t>Entrer votre nom d'utilisateur dans "nom d'utilisateur" et vôtre mot de passe précédement créer dans "Mot de passe"</t>
+  </si>
+  <si>
+    <t>Les entrées nom d'utilisateur, mot de passe doit voit être remplies</t>
+  </si>
+  <si>
+    <t>Cliquer sur le bouton "Se Connecter"</t>
+  </si>
+  <si>
+    <t>nom d'utilisateur, mot de passe utilisateur</t>
+  </si>
+  <si>
+    <t>Un pop up devrait s'afficher "Connecté ! Bienvenue matisse"</t>
+  </si>
+  <si>
+    <t>Appyuer sur le bouton "OK"</t>
+  </si>
+  <si>
+    <t>redirection vers http://C206-03:3000/chat_general.html</t>
+  </si>
+  <si>
+    <t>Scénario 7.</t>
+  </si>
+  <si>
+    <t>Message privés</t>
+  </si>
+  <si>
+    <t>Cliquer sur le pseudo d'un utilisateur connecté à la droite de l'écran, dans la colone "en ligne"</t>
+  </si>
+  <si>
+    <t>Ouverture dans la colonne "Messages privés" d'une discution entre l'utilisateur et la personne a qui on veut discuter, une bar en bas de la discution apparait</t>
+  </si>
+  <si>
+    <t>Entrer le message souhaiter dans "Envoie un message privé à …"</t>
+  </si>
+  <si>
+    <t>Entrer le message voulu</t>
+  </si>
+  <si>
+    <t>L'entrée est remplies par le texte souhaité</t>
+  </si>
+  <si>
+    <t>Appyuer sur le bouton "Envoyer"</t>
+  </si>
+  <si>
+    <t>Le texte devrait apparaitre sur le haut de l'écran a droite</t>
+  </si>
+  <si>
+    <t>Message publiques</t>
+  </si>
+  <si>
+    <t>Sur la gauche, appuyer sur "serveur", symboliser avec le logo LaDiscorde, il y en a 3</t>
+  </si>
+  <si>
+    <t>Ouverture de 3 salons au choix</t>
+  </si>
+  <si>
+    <t>Sur la gauche, appuyer sur un salon au choix, symboliser avec un emojie et du texte</t>
+  </si>
+  <si>
+    <t>Appuyer sur le salon voulu</t>
+  </si>
+  <si>
+    <t>Une séction de discution entre l'utilisateur s'ouvre, en bas de la discution apparait</t>
+  </si>
+  <si>
+    <t>Entrer le message souhaiter dans "Ecris un message dans …"</t>
   </si>
 </sst>
 </file>
@@ -455,7 +560,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="69">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -512,6 +617,57 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -539,47 +695,14 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -593,6 +716,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -620,15 +749,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -636,27 +756,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -993,7 +1092,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E692836E-065C-4DA9-AE7D-E8BAD5876E51}">
-  <dimension ref="A1:H73"/>
+  <dimension ref="A1:H170"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24.7109375" customWidth="1"/>
@@ -1011,11 +1110,11 @@
       <c r="B1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C1" s="62" t="s">
+      <c r="C1" s="53" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="62"/>
-      <c r="E1" s="62"/>
+      <c r="D1" s="53"/>
+      <c r="E1" s="53"/>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
     </row>
@@ -1033,11 +1132,11 @@
       <c r="B3" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="43" t="s">
+      <c r="C3" s="49" t="s">
         <v>25</v>
       </c>
-      <c r="D3" s="43"/>
-      <c r="E3" s="43"/>
+      <c r="D3" s="49"/>
+      <c r="E3" s="49"/>
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
     </row>
@@ -1073,12 +1172,12 @@
       <c r="B7" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="44" t="s">
+      <c r="C7" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="D7" s="44"/>
-      <c r="E7" s="44"/>
-      <c r="F7" s="45"/>
+      <c r="D7" s="50"/>
+      <c r="E7" s="50"/>
+      <c r="F7" s="51"/>
       <c r="G7" s="2"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -1086,12 +1185,12 @@
       <c r="B8" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="63" t="s">
+      <c r="C8" s="54" t="s">
         <v>26</v>
       </c>
-      <c r="D8" s="63"/>
-      <c r="E8" s="63"/>
-      <c r="F8" s="63"/>
+      <c r="D8" s="54"/>
+      <c r="E8" s="54"/>
+      <c r="F8" s="54"/>
       <c r="G8" s="2"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -1099,10 +1198,10 @@
       <c r="B9" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="63"/>
-      <c r="D9" s="63"/>
-      <c r="E9" s="63"/>
-      <c r="F9" s="63"/>
+      <c r="C9" s="54"/>
+      <c r="D9" s="54"/>
+      <c r="E9" s="54"/>
+      <c r="F9" s="54"/>
       <c r="G9" s="2"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -1110,23 +1209,23 @@
       <c r="B10" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="63" t="s">
+      <c r="C10" s="54" t="s">
         <v>27</v>
       </c>
-      <c r="D10" s="63"/>
-      <c r="E10" s="63"/>
-      <c r="F10" s="63"/>
+      <c r="D10" s="54"/>
+      <c r="E10" s="54"/>
+      <c r="F10" s="54"/>
       <c r="G10" s="2"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="2"/>
-      <c r="B11" s="56" t="s">
+      <c r="B11" s="46" t="s">
         <v>7</v>
       </c>
-      <c r="C11" s="57"/>
-      <c r="D11" s="57"/>
-      <c r="E11" s="57"/>
-      <c r="F11" s="58"/>
+      <c r="C11" s="47"/>
+      <c r="D11" s="47"/>
+      <c r="E11" s="47"/>
+      <c r="F11" s="48"/>
       <c r="G11" s="2"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -1167,11 +1266,11 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="2"/>
-      <c r="B14" s="47"/>
-      <c r="C14" s="48"/>
-      <c r="D14" s="48"/>
-      <c r="E14" s="48"/>
-      <c r="F14" s="49"/>
+      <c r="B14" s="55"/>
+      <c r="C14" s="56"/>
+      <c r="D14" s="56"/>
+      <c r="E14" s="56"/>
+      <c r="F14" s="57"/>
       <c r="G14" s="2"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -1191,75 +1290,75 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="2"/>
-      <c r="B16" s="53" t="s">
+      <c r="B16" s="61" t="s">
         <v>17</v>
       </c>
-      <c r="C16" s="54"/>
-      <c r="D16" s="54"/>
-      <c r="E16" s="54"/>
-      <c r="F16" s="55"/>
+      <c r="C16" s="62"/>
+      <c r="D16" s="62"/>
+      <c r="E16" s="62"/>
+      <c r="F16" s="63"/>
       <c r="G16" s="2"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="2"/>
-      <c r="B17" s="50" t="s">
+      <c r="B17" s="58" t="s">
         <v>18</v>
       </c>
-      <c r="C17" s="51"/>
-      <c r="D17" s="51"/>
-      <c r="E17" s="51"/>
-      <c r="F17" s="52"/>
+      <c r="C17" s="59"/>
+      <c r="D17" s="59"/>
+      <c r="E17" s="59"/>
+      <c r="F17" s="60"/>
       <c r="G17" s="2"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
-      <c r="B18" s="32" t="s">
+      <c r="B18" s="23" t="s">
         <v>19</v>
       </c>
-      <c r="C18" s="33"/>
-      <c r="D18" s="33"/>
-      <c r="E18" s="33"/>
-      <c r="F18" s="34"/>
+      <c r="C18" s="24"/>
+      <c r="D18" s="24"/>
+      <c r="E18" s="24"/>
+      <c r="F18" s="25"/>
       <c r="G18" s="2"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="2"/>
-      <c r="B19" s="35" t="s">
+      <c r="B19" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="C19" s="36"/>
-      <c r="D19" s="36"/>
-      <c r="E19" s="36"/>
-      <c r="F19" s="37"/>
+      <c r="C19" s="27"/>
+      <c r="D19" s="27"/>
+      <c r="E19" s="27"/>
+      <c r="F19" s="28"/>
       <c r="G19" s="2"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="2"/>
-      <c r="B20" s="20" t="s">
+      <c r="B20" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="C20" s="21"/>
-      <c r="D20" s="21"/>
-      <c r="E20" s="21"/>
-      <c r="F20" s="22"/>
+      <c r="C20" s="38"/>
+      <c r="D20" s="38"/>
+      <c r="E20" s="38"/>
+      <c r="F20" s="39"/>
       <c r="G20" s="2"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="2"/>
-      <c r="B21" s="23"/>
-      <c r="C21" s="24"/>
-      <c r="D21" s="24"/>
-      <c r="E21" s="24"/>
-      <c r="F21" s="25"/>
+      <c r="B21" s="40"/>
+      <c r="C21" s="41"/>
+      <c r="D21" s="41"/>
+      <c r="E21" s="41"/>
+      <c r="F21" s="42"/>
       <c r="G21" s="2"/>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="2"/>
-      <c r="B22" s="26"/>
-      <c r="C22" s="27"/>
-      <c r="D22" s="27"/>
-      <c r="E22" s="27"/>
-      <c r="F22" s="28"/>
+      <c r="B22" s="43"/>
+      <c r="C22" s="44"/>
+      <c r="D22" s="44"/>
+      <c r="E22" s="44"/>
+      <c r="F22" s="45"/>
       <c r="G22" s="2"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
@@ -1267,24 +1366,24 @@
       <c r="G23" s="2"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="41" t="s">
+      <c r="A24" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="B24" s="42"/>
-      <c r="C24" s="42"/>
-      <c r="D24" s="42"/>
-      <c r="E24" s="42"/>
-      <c r="F24" s="42"/>
-      <c r="G24" s="42"/>
+      <c r="B24" s="36"/>
+      <c r="C24" s="36"/>
+      <c r="D24" s="36"/>
+      <c r="E24" s="36"/>
+      <c r="F24" s="36"/>
+      <c r="G24" s="36"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="41"/>
-      <c r="B26" s="42"/>
-      <c r="C26" s="42"/>
-      <c r="D26" s="42"/>
-      <c r="E26" s="42"/>
-      <c r="F26" s="42"/>
-      <c r="G26" s="42"/>
+      <c r="A26" s="35"/>
+      <c r="B26" s="36"/>
+      <c r="C26" s="36"/>
+      <c r="D26" s="36"/>
+      <c r="E26" s="36"/>
+      <c r="F26" s="36"/>
+      <c r="G26" s="36"/>
     </row>
     <row r="27" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
@@ -1293,12 +1392,12 @@
       <c r="B27" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C27" s="43" t="s">
+      <c r="C27" s="49" t="s">
         <v>31</v>
       </c>
-      <c r="D27" s="43"/>
-      <c r="E27" s="43"/>
-      <c r="F27" s="43"/>
+      <c r="D27" s="49"/>
+      <c r="E27" s="49"/>
+      <c r="F27" s="49"/>
       <c r="G27" s="2"/>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
@@ -1315,12 +1414,12 @@
       <c r="B29" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="C29" s="44" t="s">
+      <c r="C29" s="50" t="s">
         <v>23</v>
       </c>
-      <c r="D29" s="44"/>
-      <c r="E29" s="44"/>
-      <c r="F29" s="45"/>
+      <c r="D29" s="50"/>
+      <c r="E29" s="50"/>
+      <c r="F29" s="51"/>
       <c r="G29" s="2"/>
       <c r="H29" s="17"/>
     </row>
@@ -1329,12 +1428,12 @@
       <c r="B30" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C30" s="46" t="s">
+      <c r="C30" s="52" t="s">
         <v>31</v>
       </c>
-      <c r="D30" s="46"/>
-      <c r="E30" s="46"/>
-      <c r="F30" s="46"/>
+      <c r="D30" s="52"/>
+      <c r="E30" s="52"/>
+      <c r="F30" s="52"/>
       <c r="G30" s="2"/>
       <c r="H30" s="17"/>
     </row>
@@ -1343,10 +1442,10 @@
       <c r="B31" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="C31" s="46"/>
-      <c r="D31" s="46"/>
-      <c r="E31" s="46"/>
-      <c r="F31" s="46"/>
+      <c r="C31" s="52"/>
+      <c r="D31" s="52"/>
+      <c r="E31" s="52"/>
+      <c r="F31" s="52"/>
       <c r="G31" s="2"/>
       <c r="H31" s="17"/>
     </row>
@@ -1355,24 +1454,24 @@
       <c r="B32" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C32" s="46" t="s">
+      <c r="C32" s="52" t="s">
         <v>32</v>
       </c>
-      <c r="D32" s="46"/>
-      <c r="E32" s="46"/>
-      <c r="F32" s="46"/>
+      <c r="D32" s="52"/>
+      <c r="E32" s="52"/>
+      <c r="F32" s="52"/>
       <c r="G32" s="2"/>
       <c r="H32" s="17"/>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="2"/>
-      <c r="B33" s="56" t="s">
+      <c r="B33" s="46" t="s">
         <v>7</v>
       </c>
-      <c r="C33" s="57"/>
-      <c r="D33" s="57"/>
-      <c r="E33" s="57"/>
-      <c r="F33" s="58"/>
+      <c r="C33" s="47"/>
+      <c r="D33" s="47"/>
+      <c r="E33" s="47"/>
+      <c r="F33" s="48"/>
       <c r="G33" s="2"/>
       <c r="H33" s="17"/>
     </row>
@@ -1452,11 +1551,11 @@
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" s="2"/>
-      <c r="B38" s="59"/>
-      <c r="C38" s="60"/>
-      <c r="D38" s="60"/>
-      <c r="E38" s="60"/>
-      <c r="F38" s="61"/>
+      <c r="B38" s="64"/>
+      <c r="C38" s="65"/>
+      <c r="D38" s="65"/>
+      <c r="E38" s="65"/>
+      <c r="F38" s="66"/>
       <c r="G38" s="2"/>
       <c r="H38" s="17"/>
     </row>
@@ -1478,81 +1577,81 @@
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="2"/>
-      <c r="B40" s="38" t="s">
+      <c r="B40" s="29" t="s">
         <v>17</v>
       </c>
-      <c r="C40" s="39"/>
-      <c r="D40" s="39"/>
-      <c r="E40" s="39"/>
-      <c r="F40" s="40"/>
+      <c r="C40" s="30"/>
+      <c r="D40" s="30"/>
+      <c r="E40" s="30"/>
+      <c r="F40" s="31"/>
       <c r="G40" s="2"/>
       <c r="H40" s="17"/>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="2"/>
-      <c r="B41" s="29" t="s">
+      <c r="B41" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="C41" s="30"/>
-      <c r="D41" s="30"/>
-      <c r="E41" s="30"/>
-      <c r="F41" s="31"/>
+      <c r="C41" s="21"/>
+      <c r="D41" s="21"/>
+      <c r="E41" s="21"/>
+      <c r="F41" s="22"/>
       <c r="G41" s="2"/>
       <c r="H41" s="17"/>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="2"/>
-      <c r="B42" s="32" t="s">
+      <c r="B42" s="23" t="s">
         <v>19</v>
       </c>
-      <c r="C42" s="33"/>
-      <c r="D42" s="33"/>
-      <c r="E42" s="33"/>
-      <c r="F42" s="34"/>
+      <c r="C42" s="24"/>
+      <c r="D42" s="24"/>
+      <c r="E42" s="24"/>
+      <c r="F42" s="25"/>
       <c r="G42" s="2"/>
       <c r="H42" s="17"/>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="2"/>
-      <c r="B43" s="35" t="s">
+      <c r="B43" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="C43" s="36"/>
-      <c r="D43" s="36"/>
-      <c r="E43" s="36"/>
-      <c r="F43" s="37"/>
+      <c r="C43" s="27"/>
+      <c r="D43" s="27"/>
+      <c r="E43" s="27"/>
+      <c r="F43" s="28"/>
       <c r="G43" s="2"/>
       <c r="H43" s="17"/>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="2"/>
-      <c r="B44" s="20" t="s">
+      <c r="B44" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="C44" s="21"/>
-      <c r="D44" s="21"/>
-      <c r="E44" s="21"/>
-      <c r="F44" s="22"/>
+      <c r="C44" s="38"/>
+      <c r="D44" s="38"/>
+      <c r="E44" s="38"/>
+      <c r="F44" s="39"/>
       <c r="G44" s="2"/>
       <c r="H44" s="17"/>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" s="2"/>
-      <c r="B45" s="23"/>
-      <c r="C45" s="24"/>
-      <c r="D45" s="24"/>
-      <c r="E45" s="24"/>
-      <c r="F45" s="25"/>
+      <c r="B45" s="40"/>
+      <c r="C45" s="41"/>
+      <c r="D45" s="41"/>
+      <c r="E45" s="41"/>
+      <c r="F45" s="42"/>
       <c r="G45" s="2"/>
       <c r="H45" s="17"/>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" s="2"/>
-      <c r="B46" s="26"/>
-      <c r="C46" s="27"/>
-      <c r="D46" s="27"/>
-      <c r="E46" s="27"/>
-      <c r="F46" s="28"/>
+      <c r="B46" s="43"/>
+      <c r="C46" s="44"/>
+      <c r="D46" s="44"/>
+      <c r="E46" s="44"/>
+      <c r="F46" s="45"/>
       <c r="G46" s="2"/>
       <c r="H46" s="17"/>
     </row>
@@ -1570,15 +1669,15 @@
       <c r="H48" s="17"/>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A49" s="41" t="s">
+      <c r="A49" s="35" t="s">
         <v>39</v>
       </c>
-      <c r="B49" s="42"/>
-      <c r="C49" s="42"/>
-      <c r="D49" s="42"/>
-      <c r="E49" s="42"/>
-      <c r="F49" s="42"/>
-      <c r="G49" s="42"/>
+      <c r="B49" s="36"/>
+      <c r="C49" s="36"/>
+      <c r="D49" s="36"/>
+      <c r="E49" s="36"/>
+      <c r="F49" s="36"/>
+      <c r="G49" s="36"/>
     </row>
     <row r="52" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
@@ -1587,12 +1686,12 @@
       <c r="B52" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C52" s="43" t="s">
+      <c r="C52" s="49" t="s">
         <v>42</v>
       </c>
-      <c r="D52" s="43"/>
-      <c r="E52" s="43"/>
-      <c r="F52" s="43"/>
+      <c r="D52" s="49"/>
+      <c r="E52" s="49"/>
+      <c r="F52" s="49"/>
       <c r="G52" s="2"/>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
@@ -1609,12 +1708,12 @@
       <c r="B54" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="C54" s="44" t="s">
+      <c r="C54" s="50" t="s">
         <v>23</v>
       </c>
-      <c r="D54" s="44"/>
-      <c r="E54" s="44"/>
-      <c r="F54" s="45"/>
+      <c r="D54" s="50"/>
+      <c r="E54" s="50"/>
+      <c r="F54" s="51"/>
       <c r="G54" s="2"/>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
@@ -1622,12 +1721,12 @@
       <c r="B55" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C55" s="46" t="s">
+      <c r="C55" s="52" t="s">
         <v>31</v>
       </c>
-      <c r="D55" s="46"/>
-      <c r="E55" s="46"/>
-      <c r="F55" s="46"/>
+      <c r="D55" s="52"/>
+      <c r="E55" s="52"/>
+      <c r="F55" s="52"/>
       <c r="G55" s="2"/>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
@@ -1635,10 +1734,10 @@
       <c r="B56" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="C56" s="46"/>
-      <c r="D56" s="46"/>
-      <c r="E56" s="46"/>
-      <c r="F56" s="46"/>
+      <c r="C56" s="52"/>
+      <c r="D56" s="52"/>
+      <c r="E56" s="52"/>
+      <c r="F56" s="52"/>
       <c r="G56" s="2"/>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
@@ -1646,23 +1745,23 @@
       <c r="B57" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C57" s="46" t="s">
+      <c r="C57" s="52" t="s">
         <v>43</v>
       </c>
-      <c r="D57" s="46"/>
-      <c r="E57" s="46"/>
-      <c r="F57" s="46"/>
+      <c r="D57" s="52"/>
+      <c r="E57" s="52"/>
+      <c r="F57" s="52"/>
       <c r="G57" s="2"/>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" s="2"/>
-      <c r="B58" s="56" t="s">
+      <c r="B58" s="46" t="s">
         <v>7</v>
       </c>
-      <c r="C58" s="57"/>
-      <c r="D58" s="57"/>
-      <c r="E58" s="57"/>
-      <c r="F58" s="58"/>
+      <c r="C58" s="47"/>
+      <c r="D58" s="47"/>
+      <c r="E58" s="47"/>
+      <c r="F58" s="48"/>
       <c r="G58" s="2"/>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
@@ -1722,11 +1821,11 @@
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" s="2"/>
-      <c r="B62" s="66"/>
-      <c r="C62" s="67"/>
-      <c r="D62" s="67"/>
-      <c r="E62" s="67"/>
-      <c r="F62" s="68"/>
+      <c r="B62" s="32"/>
+      <c r="C62" s="33"/>
+      <c r="D62" s="33"/>
+      <c r="E62" s="33"/>
+      <c r="F62" s="34"/>
       <c r="G62" s="2"/>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
@@ -1746,75 +1845,75 @@
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" s="2"/>
-      <c r="B64" s="38" t="s">
+      <c r="B64" s="29" t="s">
         <v>17</v>
       </c>
-      <c r="C64" s="39"/>
-      <c r="D64" s="39"/>
-      <c r="E64" s="39"/>
-      <c r="F64" s="40"/>
+      <c r="C64" s="30"/>
+      <c r="D64" s="30"/>
+      <c r="E64" s="30"/>
+      <c r="F64" s="31"/>
       <c r="G64" s="2"/>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" s="2"/>
-      <c r="B65" s="29" t="s">
+      <c r="B65" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="C65" s="30"/>
-      <c r="D65" s="30"/>
-      <c r="E65" s="30"/>
-      <c r="F65" s="31"/>
+      <c r="C65" s="21"/>
+      <c r="D65" s="21"/>
+      <c r="E65" s="21"/>
+      <c r="F65" s="22"/>
       <c r="G65" s="2"/>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" s="2"/>
-      <c r="B66" s="32" t="s">
+      <c r="B66" s="23" t="s">
         <v>19</v>
       </c>
-      <c r="C66" s="65"/>
-      <c r="D66" s="65"/>
-      <c r="E66" s="65"/>
-      <c r="F66" s="34"/>
+      <c r="C66" s="24"/>
+      <c r="D66" s="24"/>
+      <c r="E66" s="24"/>
+      <c r="F66" s="25"/>
       <c r="G66" s="2"/>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" s="2"/>
-      <c r="B67" s="35" t="s">
+      <c r="B67" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="C67" s="36"/>
-      <c r="D67" s="36"/>
-      <c r="E67" s="36"/>
-      <c r="F67" s="37"/>
+      <c r="C67" s="27"/>
+      <c r="D67" s="27"/>
+      <c r="E67" s="27"/>
+      <c r="F67" s="28"/>
       <c r="G67" s="2"/>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" s="2"/>
-      <c r="B68" s="20" t="s">
+      <c r="B68" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="C68" s="21"/>
-      <c r="D68" s="21"/>
-      <c r="E68" s="21"/>
-      <c r="F68" s="22"/>
+      <c r="C68" s="38"/>
+      <c r="D68" s="38"/>
+      <c r="E68" s="38"/>
+      <c r="F68" s="39"/>
       <c r="G68" s="2"/>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" s="2"/>
-      <c r="B69" s="23"/>
-      <c r="C69" s="64"/>
-      <c r="D69" s="64"/>
-      <c r="E69" s="64"/>
-      <c r="F69" s="25"/>
+      <c r="B69" s="40"/>
+      <c r="C69" s="41"/>
+      <c r="D69" s="41"/>
+      <c r="E69" s="41"/>
+      <c r="F69" s="42"/>
       <c r="G69" s="2"/>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" s="2"/>
-      <c r="B70" s="26"/>
-      <c r="C70" s="27"/>
-      <c r="D70" s="27"/>
-      <c r="E70" s="27"/>
-      <c r="F70" s="28"/>
+      <c r="B70" s="43"/>
+      <c r="C70" s="44"/>
+      <c r="D70" s="44"/>
+      <c r="E70" s="44"/>
+      <c r="F70" s="45"/>
       <c r="G70" s="2"/>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
@@ -1822,38 +1921,1168 @@
       <c r="G71" s="2"/>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A73" s="41" t="s">
+      <c r="A73" s="35" t="s">
         <v>44</v>
       </c>
-      <c r="B73" s="42"/>
-      <c r="C73" s="42"/>
-      <c r="D73" s="42"/>
-      <c r="E73" s="42"/>
-      <c r="F73" s="42"/>
-      <c r="G73" s="42"/>
+      <c r="B73" s="36"/>
+      <c r="C73" s="36"/>
+      <c r="D73" s="36"/>
+      <c r="E73" s="36"/>
+      <c r="F73" s="36"/>
+      <c r="G73" s="36"/>
+    </row>
+    <row r="75" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A75" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B75" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C75" s="49" t="s">
+        <v>54</v>
+      </c>
+      <c r="D75" s="49"/>
+      <c r="E75" s="49"/>
+      <c r="F75" s="49"/>
+      <c r="G75" s="2"/>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A76" s="2"/>
+      <c r="B76" s="2"/>
+      <c r="C76" s="2"/>
+      <c r="D76" s="2"/>
+      <c r="E76" s="2"/>
+      <c r="F76" s="2"/>
+      <c r="G76" s="2"/>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A77" s="2"/>
+      <c r="B77" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="C77" s="50" t="s">
+        <v>23</v>
+      </c>
+      <c r="D77" s="50"/>
+      <c r="E77" s="50"/>
+      <c r="F77" s="51"/>
+      <c r="G77" s="2"/>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A78" s="2"/>
+      <c r="B78" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C78" s="52" t="s">
+        <v>31</v>
+      </c>
+      <c r="D78" s="52"/>
+      <c r="E78" s="52"/>
+      <c r="F78" s="52"/>
+      <c r="G78" s="2"/>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A79" s="2"/>
+      <c r="B79" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C79" s="52"/>
+      <c r="D79" s="52"/>
+      <c r="E79" s="52"/>
+      <c r="F79" s="52"/>
+      <c r="G79" s="2"/>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A80" s="2"/>
+      <c r="B80" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C80" s="52" t="s">
+        <v>51</v>
+      </c>
+      <c r="D80" s="52"/>
+      <c r="E80" s="52"/>
+      <c r="F80" s="52"/>
+      <c r="G80" s="2"/>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A81" s="2"/>
+      <c r="B81" s="46" t="s">
+        <v>7</v>
+      </c>
+      <c r="C81" s="47"/>
+      <c r="D81" s="47"/>
+      <c r="E81" s="47"/>
+      <c r="F81" s="48"/>
+      <c r="G81" s="2"/>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A82" s="2"/>
+      <c r="B82" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="C82" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="D82" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="E82" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="F82" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G82" s="2"/>
+    </row>
+    <row r="83" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A83" s="2"/>
+      <c r="B83" s="5">
+        <v>1</v>
+      </c>
+      <c r="C83" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D83" s="5"/>
+      <c r="E83" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="F83" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G83" s="2"/>
+    </row>
+    <row r="84" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+      <c r="A84" s="2"/>
+      <c r="B84" s="8">
+        <v>2</v>
+      </c>
+      <c r="C84" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D84" s="9"/>
+      <c r="E84" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="F84" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G84" s="2"/>
+    </row>
+    <row r="85" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A85" s="2"/>
+      <c r="B85" s="8">
+        <v>3</v>
+      </c>
+      <c r="C85" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="D85" s="9"/>
+      <c r="E85" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="F85" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G85" s="2"/>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A86" s="2"/>
+      <c r="B86" s="32"/>
+      <c r="C86" s="33"/>
+      <c r="D86" s="33"/>
+      <c r="E86" s="33"/>
+      <c r="F86" s="34"/>
+      <c r="G86" s="2"/>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A87" s="2"/>
+      <c r="B87" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="C87" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="D87" s="19"/>
+      <c r="E87" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="F87" s="19"/>
+      <c r="G87" s="2"/>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A88" s="2"/>
+      <c r="B88" s="29" t="s">
+        <v>17</v>
+      </c>
+      <c r="C88" s="30"/>
+      <c r="D88" s="30"/>
+      <c r="E88" s="30"/>
+      <c r="F88" s="31"/>
+      <c r="G88" s="2"/>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A89" s="2"/>
+      <c r="B89" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="C89" s="21"/>
+      <c r="D89" s="21"/>
+      <c r="E89" s="21"/>
+      <c r="F89" s="22"/>
+      <c r="G89" s="2"/>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A90" s="2"/>
+      <c r="B90" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="C90" s="24"/>
+      <c r="D90" s="24"/>
+      <c r="E90" s="24"/>
+      <c r="F90" s="25"/>
+      <c r="G90" s="2"/>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A91" s="2"/>
+      <c r="B91" s="26" t="s">
+        <v>20</v>
+      </c>
+      <c r="C91" s="27"/>
+      <c r="D91" s="27"/>
+      <c r="E91" s="27"/>
+      <c r="F91" s="28"/>
+      <c r="G91" s="2"/>
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A92" s="2"/>
+      <c r="B92" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="C92" s="38"/>
+      <c r="D92" s="38"/>
+      <c r="E92" s="38"/>
+      <c r="F92" s="39"/>
+      <c r="G92" s="2"/>
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A93" s="2"/>
+      <c r="B93" s="40"/>
+      <c r="C93" s="41"/>
+      <c r="D93" s="41"/>
+      <c r="E93" s="41"/>
+      <c r="F93" s="42"/>
+      <c r="G93" s="2"/>
+    </row>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A94" s="2"/>
+      <c r="B94" s="43"/>
+      <c r="C94" s="44"/>
+      <c r="D94" s="44"/>
+      <c r="E94" s="44"/>
+      <c r="F94" s="45"/>
+      <c r="G94" s="2"/>
+    </row>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A95" s="2"/>
+      <c r="G95" s="2"/>
+    </row>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A97" s="35" t="s">
+        <v>44</v>
+      </c>
+      <c r="B97" s="36"/>
+      <c r="C97" s="36"/>
+      <c r="D97" s="36"/>
+      <c r="E97" s="36"/>
+      <c r="F97" s="36"/>
+      <c r="G97" s="36"/>
+    </row>
+    <row r="99" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A99" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B99" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C99" s="49" t="s">
+        <v>61</v>
+      </c>
+      <c r="D99" s="49"/>
+      <c r="E99" s="49"/>
+      <c r="F99" s="49"/>
+      <c r="G99" s="2"/>
+    </row>
+    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A100" s="2"/>
+      <c r="B100" s="2"/>
+      <c r="C100" s="2"/>
+      <c r="D100" s="2"/>
+      <c r="E100" s="2"/>
+      <c r="F100" s="2"/>
+      <c r="G100" s="2"/>
+    </row>
+    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A101" s="2"/>
+      <c r="B101" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="C101" s="50" t="s">
+        <v>23</v>
+      </c>
+      <c r="D101" s="50"/>
+      <c r="E101" s="50"/>
+      <c r="F101" s="51"/>
+      <c r="G101" s="2"/>
+    </row>
+    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A102" s="2"/>
+      <c r="B102" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C102" s="52" t="s">
+        <v>31</v>
+      </c>
+      <c r="D102" s="52"/>
+      <c r="E102" s="52"/>
+      <c r="F102" s="52"/>
+      <c r="G102" s="2"/>
+    </row>
+    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A103" s="2"/>
+      <c r="B103" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C103" s="52"/>
+      <c r="D103" s="52"/>
+      <c r="E103" s="52"/>
+      <c r="F103" s="52"/>
+      <c r="G103" s="2"/>
+    </row>
+    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A104" s="2"/>
+      <c r="B104" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C104" s="52" t="s">
+        <v>51</v>
+      </c>
+      <c r="D104" s="52"/>
+      <c r="E104" s="52"/>
+      <c r="F104" s="52"/>
+      <c r="G104" s="2"/>
+    </row>
+    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A105" s="2"/>
+      <c r="B105" s="46" t="s">
+        <v>7</v>
+      </c>
+      <c r="C105" s="47"/>
+      <c r="D105" s="47"/>
+      <c r="E105" s="47"/>
+      <c r="F105" s="48"/>
+      <c r="G105" s="2"/>
+    </row>
+    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A106" s="2"/>
+      <c r="B106" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="C106" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="D106" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="E106" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="F106" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G106" s="2"/>
+    </row>
+    <row r="107" spans="1:7" ht="90" x14ac:dyDescent="0.25">
+      <c r="A107" s="2"/>
+      <c r="B107" s="5">
+        <v>1</v>
+      </c>
+      <c r="C107" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="D107" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="E107" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="F107" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G107" s="2"/>
+    </row>
+    <row r="108" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A108" s="2"/>
+      <c r="B108" s="8">
+        <v>2</v>
+      </c>
+      <c r="C108" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="D108" s="9"/>
+      <c r="E108" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="F108" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G108" s="2"/>
+    </row>
+    <row r="109" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A109" s="2"/>
+      <c r="B109" s="8">
+        <v>3</v>
+      </c>
+      <c r="C109" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="D109" s="9"/>
+      <c r="E109" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="F109" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G109" s="2"/>
+    </row>
+    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A110" s="2"/>
+      <c r="B110" s="32"/>
+      <c r="C110" s="33"/>
+      <c r="D110" s="33"/>
+      <c r="E110" s="33"/>
+      <c r="F110" s="34"/>
+      <c r="G110" s="2"/>
+    </row>
+    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A111" s="2"/>
+      <c r="B111" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="C111" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="D111" s="19"/>
+      <c r="E111" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="F111" s="19"/>
+      <c r="G111" s="2"/>
+    </row>
+    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A112" s="2"/>
+      <c r="B112" s="29" t="s">
+        <v>17</v>
+      </c>
+      <c r="C112" s="30"/>
+      <c r="D112" s="30"/>
+      <c r="E112" s="30"/>
+      <c r="F112" s="31"/>
+      <c r="G112" s="2"/>
+    </row>
+    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A113" s="2"/>
+      <c r="B113" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="C113" s="21"/>
+      <c r="D113" s="21"/>
+      <c r="E113" s="21"/>
+      <c r="F113" s="22"/>
+      <c r="G113" s="2"/>
+    </row>
+    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A114" s="2"/>
+      <c r="B114" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="C114" s="24"/>
+      <c r="D114" s="24"/>
+      <c r="E114" s="24"/>
+      <c r="F114" s="25"/>
+      <c r="G114" s="2"/>
+    </row>
+    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A115" s="2"/>
+      <c r="B115" s="26" t="s">
+        <v>20</v>
+      </c>
+      <c r="C115" s="27"/>
+      <c r="D115" s="27"/>
+      <c r="E115" s="27"/>
+      <c r="F115" s="28"/>
+      <c r="G115" s="2"/>
+    </row>
+    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A116" s="2"/>
+      <c r="B116" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="C116" s="38"/>
+      <c r="D116" s="38"/>
+      <c r="E116" s="38"/>
+      <c r="F116" s="39"/>
+      <c r="G116" s="2"/>
+    </row>
+    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A117" s="2"/>
+      <c r="B117" s="40"/>
+      <c r="C117" s="41"/>
+      <c r="D117" s="41"/>
+      <c r="E117" s="41"/>
+      <c r="F117" s="42"/>
+      <c r="G117" s="2"/>
+    </row>
+    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A118" s="2"/>
+      <c r="B118" s="43"/>
+      <c r="C118" s="44"/>
+      <c r="D118" s="44"/>
+      <c r="E118" s="44"/>
+      <c r="F118" s="45"/>
+      <c r="G118" s="2"/>
+    </row>
+    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A119" s="2"/>
+      <c r="G119" s="2"/>
+    </row>
+    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A121" s="35" t="s">
+        <v>44</v>
+      </c>
+      <c r="B121" s="36"/>
+      <c r="C121" s="36"/>
+      <c r="D121" s="36"/>
+      <c r="E121" s="36"/>
+      <c r="F121" s="36"/>
+      <c r="G121" s="36"/>
+    </row>
+    <row r="123" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A123" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B123" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="C123" s="49" t="s">
+        <v>70</v>
+      </c>
+      <c r="D123" s="49"/>
+      <c r="E123" s="49"/>
+      <c r="F123" s="49"/>
+      <c r="G123" s="2"/>
+    </row>
+    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A124" s="2"/>
+      <c r="B124" s="2"/>
+      <c r="C124" s="2"/>
+      <c r="D124" s="2"/>
+      <c r="E124" s="2"/>
+      <c r="F124" s="2"/>
+      <c r="G124" s="2"/>
+    </row>
+    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A125" s="2"/>
+      <c r="B125" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="C125" s="50" t="s">
+        <v>23</v>
+      </c>
+      <c r="D125" s="50"/>
+      <c r="E125" s="50"/>
+      <c r="F125" s="51"/>
+      <c r="G125" s="2"/>
+    </row>
+    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A126" s="2"/>
+      <c r="B126" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C126" s="52" t="s">
+        <v>31</v>
+      </c>
+      <c r="D126" s="52"/>
+      <c r="E126" s="52"/>
+      <c r="F126" s="52"/>
+      <c r="G126" s="2"/>
+    </row>
+    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A127" s="2"/>
+      <c r="B127" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C127" s="52"/>
+      <c r="D127" s="52"/>
+      <c r="E127" s="52"/>
+      <c r="F127" s="52"/>
+      <c r="G127" s="2"/>
+    </row>
+    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A128" s="2"/>
+      <c r="B128" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C128" s="52" t="s">
+        <v>51</v>
+      </c>
+      <c r="D128" s="52"/>
+      <c r="E128" s="52"/>
+      <c r="F128" s="52"/>
+      <c r="G128" s="2"/>
+    </row>
+    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A129" s="2"/>
+      <c r="B129" s="46" t="s">
+        <v>7</v>
+      </c>
+      <c r="C129" s="47"/>
+      <c r="D129" s="47"/>
+      <c r="E129" s="47"/>
+      <c r="F129" s="48"/>
+      <c r="G129" s="2"/>
+    </row>
+    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A130" s="2"/>
+      <c r="B130" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="C130" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="D130" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="E130" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="F130" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G130" s="2"/>
+    </row>
+    <row r="131" spans="1:7" ht="90" x14ac:dyDescent="0.25">
+      <c r="A131" s="2"/>
+      <c r="B131" s="5">
+        <v>1</v>
+      </c>
+      <c r="C131" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="D131" s="7"/>
+      <c r="E131" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="F131" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G131" s="2"/>
+    </row>
+    <row r="132" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+      <c r="A132" s="2"/>
+      <c r="B132" s="8">
+        <v>2</v>
+      </c>
+      <c r="C132" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="D132" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="E132" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="F132" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G132" s="2"/>
+    </row>
+    <row r="133" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A133" s="2"/>
+      <c r="B133" s="8">
+        <v>3</v>
+      </c>
+      <c r="C133" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="D133" s="9"/>
+      <c r="E133" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="F133" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G133" s="2"/>
+    </row>
+    <row r="134" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A134" s="2"/>
+      <c r="B134" s="32"/>
+      <c r="C134" s="33"/>
+      <c r="D134" s="33"/>
+      <c r="E134" s="33"/>
+      <c r="F134" s="34"/>
+      <c r="G134" s="2"/>
+    </row>
+    <row r="135" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A135" s="2"/>
+      <c r="B135" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="C135" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="D135" s="19"/>
+      <c r="E135" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="F135" s="19"/>
+      <c r="G135" s="2"/>
+    </row>
+    <row r="136" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A136" s="2"/>
+      <c r="B136" s="29" t="s">
+        <v>17</v>
+      </c>
+      <c r="C136" s="30"/>
+      <c r="D136" s="30"/>
+      <c r="E136" s="30"/>
+      <c r="F136" s="31"/>
+      <c r="G136" s="2"/>
+    </row>
+    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A137" s="2"/>
+      <c r="B137" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="C137" s="21"/>
+      <c r="D137" s="21"/>
+      <c r="E137" s="21"/>
+      <c r="F137" s="22"/>
+      <c r="G137" s="2"/>
+    </row>
+    <row r="138" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A138" s="2"/>
+      <c r="B138" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="C138" s="24"/>
+      <c r="D138" s="24"/>
+      <c r="E138" s="24"/>
+      <c r="F138" s="25"/>
+      <c r="G138" s="2"/>
+    </row>
+    <row r="139" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A139" s="2"/>
+      <c r="B139" s="26" t="s">
+        <v>20</v>
+      </c>
+      <c r="C139" s="27"/>
+      <c r="D139" s="27"/>
+      <c r="E139" s="27"/>
+      <c r="F139" s="28"/>
+      <c r="G139" s="2"/>
+    </row>
+    <row r="140" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A140" s="2"/>
+      <c r="B140" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="C140" s="38"/>
+      <c r="D140" s="38"/>
+      <c r="E140" s="38"/>
+      <c r="F140" s="39"/>
+      <c r="G140" s="2"/>
+    </row>
+    <row r="141" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A141" s="2"/>
+      <c r="B141" s="40"/>
+      <c r="C141" s="41"/>
+      <c r="D141" s="41"/>
+      <c r="E141" s="41"/>
+      <c r="F141" s="42"/>
+      <c r="G141" s="2"/>
+    </row>
+    <row r="142" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A142" s="2"/>
+      <c r="B142" s="43"/>
+      <c r="C142" s="44"/>
+      <c r="D142" s="44"/>
+      <c r="E142" s="44"/>
+      <c r="F142" s="45"/>
+      <c r="G142" s="2"/>
+    </row>
+    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A143" s="2"/>
+      <c r="G143" s="2"/>
+    </row>
+    <row r="145" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A145" s="35" t="s">
+        <v>44</v>
+      </c>
+      <c r="B145" s="36"/>
+      <c r="C145" s="36"/>
+      <c r="D145" s="36"/>
+      <c r="E145" s="36"/>
+      <c r="F145" s="36"/>
+      <c r="G145" s="36"/>
+    </row>
+    <row r="147" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A147" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B147" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C147" s="49" t="s">
+        <v>78</v>
+      </c>
+      <c r="D147" s="49"/>
+      <c r="E147" s="49"/>
+      <c r="F147" s="49"/>
+      <c r="G147" s="2"/>
+    </row>
+    <row r="148" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A148" s="2"/>
+      <c r="B148" s="2"/>
+      <c r="C148" s="2"/>
+      <c r="D148" s="2"/>
+      <c r="E148" s="2"/>
+      <c r="F148" s="2"/>
+      <c r="G148" s="2"/>
+    </row>
+    <row r="149" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A149" s="2"/>
+      <c r="B149" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="C149" s="50" t="s">
+        <v>23</v>
+      </c>
+      <c r="D149" s="50"/>
+      <c r="E149" s="50"/>
+      <c r="F149" s="51"/>
+      <c r="G149" s="2"/>
+    </row>
+    <row r="150" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A150" s="2"/>
+      <c r="B150" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C150" s="52" t="s">
+        <v>31</v>
+      </c>
+      <c r="D150" s="52"/>
+      <c r="E150" s="52"/>
+      <c r="F150" s="52"/>
+      <c r="G150" s="2"/>
+    </row>
+    <row r="151" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A151" s="2"/>
+      <c r="B151" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C151" s="52"/>
+      <c r="D151" s="52"/>
+      <c r="E151" s="52"/>
+      <c r="F151" s="52"/>
+      <c r="G151" s="2"/>
+    </row>
+    <row r="152" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A152" s="2"/>
+      <c r="B152" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C152" s="52" t="s">
+        <v>51</v>
+      </c>
+      <c r="D152" s="52"/>
+      <c r="E152" s="52"/>
+      <c r="F152" s="52"/>
+      <c r="G152" s="2"/>
+    </row>
+    <row r="153" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A153" s="2"/>
+      <c r="B153" s="46" t="s">
+        <v>7</v>
+      </c>
+      <c r="C153" s="47"/>
+      <c r="D153" s="47"/>
+      <c r="E153" s="47"/>
+      <c r="F153" s="48"/>
+      <c r="G153" s="2"/>
+    </row>
+    <row r="154" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A154" s="2"/>
+      <c r="B154" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="C154" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="D154" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="E154" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="F154" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G154" s="2"/>
+    </row>
+    <row r="155" spans="1:7" ht="90" x14ac:dyDescent="0.25">
+      <c r="A155" s="2"/>
+      <c r="B155" s="5">
+        <v>1</v>
+      </c>
+      <c r="C155" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="D155" s="7"/>
+      <c r="E155" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="F155" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G155" s="2"/>
+    </row>
+    <row r="156" spans="1:7" ht="75" x14ac:dyDescent="0.25">
+      <c r="A156" s="2"/>
+      <c r="B156" s="8">
+        <v>2</v>
+      </c>
+      <c r="C156" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="D156" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="E156" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="F156" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G156" s="2"/>
+    </row>
+    <row r="157" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A157" s="2"/>
+      <c r="B157" s="8">
+        <v>3</v>
+      </c>
+      <c r="C157" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="D157" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="E157" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="F157" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G157" s="2"/>
+    </row>
+    <row r="158" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A158" s="2"/>
+      <c r="B158" s="8">
+        <v>4</v>
+      </c>
+      <c r="C158" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="D158" s="9"/>
+      <c r="E158" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="F158" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G158" s="2"/>
+    </row>
+    <row r="159" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A159" s="2"/>
+      <c r="B159" s="32"/>
+      <c r="C159" s="33"/>
+      <c r="D159" s="33"/>
+      <c r="E159" s="33"/>
+      <c r="F159" s="34"/>
+      <c r="G159" s="2"/>
+    </row>
+    <row r="160" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A160" s="2"/>
+      <c r="B160" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="C160" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="D160" s="19"/>
+      <c r="E160" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="F160" s="19"/>
+      <c r="G160" s="2"/>
+    </row>
+    <row r="161" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A161" s="2"/>
+      <c r="B161" s="29" t="s">
+        <v>17</v>
+      </c>
+      <c r="C161" s="30"/>
+      <c r="D161" s="30"/>
+      <c r="E161" s="30"/>
+      <c r="F161" s="31"/>
+      <c r="G161" s="2"/>
+    </row>
+    <row r="162" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A162" s="2"/>
+      <c r="B162" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="C162" s="21"/>
+      <c r="D162" s="21"/>
+      <c r="E162" s="21"/>
+      <c r="F162" s="22"/>
+      <c r="G162" s="2"/>
+    </row>
+    <row r="163" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A163" s="2"/>
+      <c r="B163" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="C163" s="24"/>
+      <c r="D163" s="24"/>
+      <c r="E163" s="24"/>
+      <c r="F163" s="25"/>
+      <c r="G163" s="2"/>
+    </row>
+    <row r="164" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A164" s="2"/>
+      <c r="B164" s="26" t="s">
+        <v>20</v>
+      </c>
+      <c r="C164" s="27"/>
+      <c r="D164" s="27"/>
+      <c r="E164" s="27"/>
+      <c r="F164" s="28"/>
+      <c r="G164" s="2"/>
+    </row>
+    <row r="165" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A165" s="2"/>
+      <c r="B165" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="C165" s="38"/>
+      <c r="D165" s="38"/>
+      <c r="E165" s="38"/>
+      <c r="F165" s="39"/>
+      <c r="G165" s="2"/>
+    </row>
+    <row r="166" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A166" s="2"/>
+      <c r="B166" s="40"/>
+      <c r="C166" s="41"/>
+      <c r="D166" s="41"/>
+      <c r="E166" s="41"/>
+      <c r="F166" s="42"/>
+      <c r="G166" s="2"/>
+    </row>
+    <row r="167" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A167" s="2"/>
+      <c r="B167" s="43"/>
+      <c r="C167" s="44"/>
+      <c r="D167" s="44"/>
+      <c r="E167" s="44"/>
+      <c r="F167" s="45"/>
+      <c r="G167" s="2"/>
+    </row>
+    <row r="168" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A168" s="2"/>
+      <c r="G168" s="2"/>
+    </row>
+    <row r="170" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A170" s="35" t="s">
+        <v>44</v>
+      </c>
+      <c r="B170" s="36"/>
+      <c r="C170" s="36"/>
+      <c r="D170" s="36"/>
+      <c r="E170" s="36"/>
+      <c r="F170" s="36"/>
+      <c r="G170" s="36"/>
     </row>
   </sheetData>
-  <mergeCells count="41">
-    <mergeCell ref="B65:F65"/>
-    <mergeCell ref="B66:F66"/>
-    <mergeCell ref="B67:F67"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B62:F62"/>
-    <mergeCell ref="A73:G73"/>
-    <mergeCell ref="B68:F70"/>
-    <mergeCell ref="B58:F58"/>
-    <mergeCell ref="C52:F52"/>
-    <mergeCell ref="C54:F54"/>
-    <mergeCell ref="C55:F55"/>
-    <mergeCell ref="C56:F56"/>
-    <mergeCell ref="C57:F57"/>
-    <mergeCell ref="B11:F11"/>
-    <mergeCell ref="C1:E1"/>
-    <mergeCell ref="C3:E3"/>
-    <mergeCell ref="C7:F7"/>
-    <mergeCell ref="C8:F8"/>
-    <mergeCell ref="C9:F9"/>
-    <mergeCell ref="C10:F10"/>
+  <mergeCells count="93">
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B163:F163"/>
+    <mergeCell ref="B164:F164"/>
+    <mergeCell ref="B165:F167"/>
+    <mergeCell ref="A170:G170"/>
+    <mergeCell ref="C151:F151"/>
+    <mergeCell ref="C152:F152"/>
+    <mergeCell ref="B153:F153"/>
+    <mergeCell ref="B159:F159"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B140:F142"/>
+    <mergeCell ref="A145:G145"/>
+    <mergeCell ref="C147:F147"/>
+    <mergeCell ref="C149:F149"/>
+    <mergeCell ref="C150:F150"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B136:F136"/>
+    <mergeCell ref="B137:F137"/>
+    <mergeCell ref="B138:F138"/>
+    <mergeCell ref="B139:F139"/>
+    <mergeCell ref="C125:F125"/>
+    <mergeCell ref="C126:F126"/>
+    <mergeCell ref="C127:F127"/>
+    <mergeCell ref="C128:F128"/>
+    <mergeCell ref="B129:F129"/>
+    <mergeCell ref="C123:F123"/>
+    <mergeCell ref="A97:G97"/>
+    <mergeCell ref="C75:F75"/>
+    <mergeCell ref="C79:F79"/>
+    <mergeCell ref="C80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B88:F88"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B90:F90"/>
+    <mergeCell ref="B91:F91"/>
+    <mergeCell ref="B92:F94"/>
+    <mergeCell ref="B86:F86"/>
+    <mergeCell ref="C77:F77"/>
+    <mergeCell ref="C78:F78"/>
+    <mergeCell ref="B115:F115"/>
+    <mergeCell ref="B116:F118"/>
+    <mergeCell ref="A121:G121"/>
+    <mergeCell ref="B105:F105"/>
+    <mergeCell ref="B110:F110"/>
+    <mergeCell ref="B112:F112"/>
+    <mergeCell ref="B113:F113"/>
+    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="C99:F99"/>
+    <mergeCell ref="C101:F101"/>
+    <mergeCell ref="C102:F102"/>
+    <mergeCell ref="C103:F103"/>
+    <mergeCell ref="C104:F104"/>
+    <mergeCell ref="B44:F46"/>
+    <mergeCell ref="B41:F41"/>
+    <mergeCell ref="B42:F42"/>
+    <mergeCell ref="B43:F43"/>
+    <mergeCell ref="B40:F40"/>
     <mergeCell ref="C32:F32"/>
     <mergeCell ref="A49:G49"/>
     <mergeCell ref="B14:F14"/>
@@ -1870,11 +3099,26 @@
     <mergeCell ref="C29:F29"/>
     <mergeCell ref="C30:F30"/>
     <mergeCell ref="C31:F31"/>
-    <mergeCell ref="B44:F46"/>
-    <mergeCell ref="B41:F41"/>
-    <mergeCell ref="B42:F42"/>
-    <mergeCell ref="B43:F43"/>
-    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="C3:E3"/>
+    <mergeCell ref="C7:F7"/>
+    <mergeCell ref="C8:F8"/>
+    <mergeCell ref="C9:F9"/>
+    <mergeCell ref="C10:F10"/>
+    <mergeCell ref="A73:G73"/>
+    <mergeCell ref="B68:F70"/>
+    <mergeCell ref="B58:F58"/>
+    <mergeCell ref="C52:F52"/>
+    <mergeCell ref="C54:F54"/>
+    <mergeCell ref="C55:F55"/>
+    <mergeCell ref="C56:F56"/>
+    <mergeCell ref="C57:F57"/>
+    <mergeCell ref="B65:F65"/>
+    <mergeCell ref="B66:F66"/>
+    <mergeCell ref="B67:F67"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B62:F62"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Plannification/Fiche_recette_LaDiscorde.xlsx
+++ b/Plannification/Fiche_recette_LaDiscorde.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\matisse.begaud\Documents\GitHub\mini_projet2\Plannification\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{515302C5-FDF2-4EA1-9EDD-8EE568592BD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFCBEE21-41E3-465F-8991-8D9462928014}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F0C29018-6AE5-422C-A279-19C0BD496EEE}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="86">
   <si>
     <t>Fiche recettes</t>
   </si>
@@ -311,6 +311,9 @@
   </si>
   <si>
     <t>Entrer le message souhaiter dans "Ecris un message dans …"</t>
+  </si>
+  <si>
+    <t>Avoir lancé la BDD / Avoir lancé le serveur / être connecter a la page/s'être authentifié</t>
   </si>
 </sst>
 </file>
@@ -644,6 +647,60 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -653,57 +710,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -713,50 +719,47 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1110,11 +1113,11 @@
       <c r="B1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C1" s="53" t="s">
+      <c r="C1" s="65" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="53"/>
-      <c r="E1" s="53"/>
+      <c r="D1" s="65"/>
+      <c r="E1" s="65"/>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
     </row>
@@ -1132,11 +1135,11 @@
       <c r="B3" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="49" t="s">
+      <c r="C3" s="50" t="s">
         <v>25</v>
       </c>
-      <c r="D3" s="49"/>
-      <c r="E3" s="49"/>
+      <c r="D3" s="50"/>
+      <c r="E3" s="50"/>
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
     </row>
@@ -1172,12 +1175,12 @@
       <c r="B7" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="50" t="s">
+      <c r="C7" s="51" t="s">
         <v>3</v>
       </c>
-      <c r="D7" s="50"/>
-      <c r="E7" s="50"/>
-      <c r="F7" s="51"/>
+      <c r="D7" s="51"/>
+      <c r="E7" s="51"/>
+      <c r="F7" s="52"/>
       <c r="G7" s="2"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -1185,12 +1188,12 @@
       <c r="B8" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="54" t="s">
+      <c r="C8" s="66" t="s">
         <v>26</v>
       </c>
-      <c r="D8" s="54"/>
-      <c r="E8" s="54"/>
-      <c r="F8" s="54"/>
+      <c r="D8" s="66"/>
+      <c r="E8" s="66"/>
+      <c r="F8" s="66"/>
       <c r="G8" s="2"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -1198,10 +1201,10 @@
       <c r="B9" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="54"/>
-      <c r="D9" s="54"/>
-      <c r="E9" s="54"/>
-      <c r="F9" s="54"/>
+      <c r="C9" s="66"/>
+      <c r="D9" s="66"/>
+      <c r="E9" s="66"/>
+      <c r="F9" s="66"/>
       <c r="G9" s="2"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -1209,23 +1212,23 @@
       <c r="B10" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="54" t="s">
+      <c r="C10" s="66" t="s">
         <v>27</v>
       </c>
-      <c r="D10" s="54"/>
-      <c r="E10" s="54"/>
-      <c r="F10" s="54"/>
+      <c r="D10" s="66"/>
+      <c r="E10" s="66"/>
+      <c r="F10" s="66"/>
       <c r="G10" s="2"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="2"/>
-      <c r="B11" s="46" t="s">
+      <c r="B11" s="41" t="s">
         <v>7</v>
       </c>
-      <c r="C11" s="47"/>
-      <c r="D11" s="47"/>
-      <c r="E11" s="47"/>
-      <c r="F11" s="48"/>
+      <c r="C11" s="42"/>
+      <c r="D11" s="42"/>
+      <c r="E11" s="42"/>
+      <c r="F11" s="43"/>
       <c r="G11" s="2"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -1266,11 +1269,11 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="2"/>
-      <c r="B14" s="55"/>
-      <c r="C14" s="56"/>
-      <c r="D14" s="56"/>
-      <c r="E14" s="56"/>
-      <c r="F14" s="57"/>
+      <c r="B14" s="53"/>
+      <c r="C14" s="54"/>
+      <c r="D14" s="54"/>
+      <c r="E14" s="54"/>
+      <c r="F14" s="55"/>
       <c r="G14" s="2"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -1290,24 +1293,24 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="2"/>
-      <c r="B16" s="61" t="s">
+      <c r="B16" s="59" t="s">
         <v>17</v>
       </c>
-      <c r="C16" s="62"/>
-      <c r="D16" s="62"/>
-      <c r="E16" s="62"/>
-      <c r="F16" s="63"/>
+      <c r="C16" s="60"/>
+      <c r="D16" s="60"/>
+      <c r="E16" s="60"/>
+      <c r="F16" s="61"/>
       <c r="G16" s="2"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="2"/>
-      <c r="B17" s="58" t="s">
+      <c r="B17" s="56" t="s">
         <v>18</v>
       </c>
-      <c r="C17" s="59"/>
-      <c r="D17" s="59"/>
-      <c r="E17" s="59"/>
-      <c r="F17" s="60"/>
+      <c r="C17" s="57"/>
+      <c r="D17" s="57"/>
+      <c r="E17" s="57"/>
+      <c r="F17" s="58"/>
       <c r="G17" s="2"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
@@ -1334,31 +1337,31 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="2"/>
-      <c r="B20" s="37" t="s">
+      <c r="B20" s="29" t="s">
         <v>21</v>
       </c>
-      <c r="C20" s="38"/>
-      <c r="D20" s="38"/>
-      <c r="E20" s="38"/>
-      <c r="F20" s="39"/>
+      <c r="C20" s="30"/>
+      <c r="D20" s="30"/>
+      <c r="E20" s="30"/>
+      <c r="F20" s="31"/>
       <c r="G20" s="2"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="2"/>
-      <c r="B21" s="40"/>
-      <c r="C21" s="41"/>
-      <c r="D21" s="41"/>
-      <c r="E21" s="41"/>
-      <c r="F21" s="42"/>
+      <c r="B21" s="32"/>
+      <c r="C21" s="33"/>
+      <c r="D21" s="33"/>
+      <c r="E21" s="33"/>
+      <c r="F21" s="34"/>
       <c r="G21" s="2"/>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="2"/>
-      <c r="B22" s="43"/>
-      <c r="C22" s="44"/>
-      <c r="D22" s="44"/>
-      <c r="E22" s="44"/>
-      <c r="F22" s="45"/>
+      <c r="B22" s="35"/>
+      <c r="C22" s="36"/>
+      <c r="D22" s="36"/>
+      <c r="E22" s="36"/>
+      <c r="F22" s="37"/>
       <c r="G22" s="2"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
@@ -1366,24 +1369,24 @@
       <c r="G23" s="2"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="35" t="s">
+      <c r="A24" s="38" t="s">
         <v>40</v>
       </c>
-      <c r="B24" s="36"/>
-      <c r="C24" s="36"/>
-      <c r="D24" s="36"/>
-      <c r="E24" s="36"/>
-      <c r="F24" s="36"/>
-      <c r="G24" s="36"/>
+      <c r="B24" s="39"/>
+      <c r="C24" s="39"/>
+      <c r="D24" s="39"/>
+      <c r="E24" s="39"/>
+      <c r="F24" s="39"/>
+      <c r="G24" s="39"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="35"/>
-      <c r="B26" s="36"/>
-      <c r="C26" s="36"/>
-      <c r="D26" s="36"/>
-      <c r="E26" s="36"/>
-      <c r="F26" s="36"/>
-      <c r="G26" s="36"/>
+      <c r="A26" s="38"/>
+      <c r="B26" s="39"/>
+      <c r="C26" s="39"/>
+      <c r="D26" s="39"/>
+      <c r="E26" s="39"/>
+      <c r="F26" s="39"/>
+      <c r="G26" s="39"/>
     </row>
     <row r="27" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
@@ -1392,12 +1395,12 @@
       <c r="B27" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C27" s="49" t="s">
+      <c r="C27" s="50" t="s">
         <v>31</v>
       </c>
-      <c r="D27" s="49"/>
-      <c r="E27" s="49"/>
-      <c r="F27" s="49"/>
+      <c r="D27" s="50"/>
+      <c r="E27" s="50"/>
+      <c r="F27" s="50"/>
       <c r="G27" s="2"/>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
@@ -1414,12 +1417,12 @@
       <c r="B29" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="C29" s="50" t="s">
+      <c r="C29" s="51" t="s">
         <v>23</v>
       </c>
-      <c r="D29" s="50"/>
-      <c r="E29" s="50"/>
-      <c r="F29" s="51"/>
+      <c r="D29" s="51"/>
+      <c r="E29" s="51"/>
+      <c r="F29" s="52"/>
       <c r="G29" s="2"/>
       <c r="H29" s="17"/>
     </row>
@@ -1428,12 +1431,12 @@
       <c r="B30" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C30" s="52" t="s">
+      <c r="C30" s="40" t="s">
         <v>31</v>
       </c>
-      <c r="D30" s="52"/>
-      <c r="E30" s="52"/>
-      <c r="F30" s="52"/>
+      <c r="D30" s="40"/>
+      <c r="E30" s="40"/>
+      <c r="F30" s="40"/>
       <c r="G30" s="2"/>
       <c r="H30" s="17"/>
     </row>
@@ -1442,10 +1445,10 @@
       <c r="B31" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="C31" s="52"/>
-      <c r="D31" s="52"/>
-      <c r="E31" s="52"/>
-      <c r="F31" s="52"/>
+      <c r="C31" s="40"/>
+      <c r="D31" s="40"/>
+      <c r="E31" s="40"/>
+      <c r="F31" s="40"/>
       <c r="G31" s="2"/>
       <c r="H31" s="17"/>
     </row>
@@ -1454,24 +1457,24 @@
       <c r="B32" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C32" s="52" t="s">
+      <c r="C32" s="40" t="s">
         <v>32</v>
       </c>
-      <c r="D32" s="52"/>
-      <c r="E32" s="52"/>
-      <c r="F32" s="52"/>
+      <c r="D32" s="40"/>
+      <c r="E32" s="40"/>
+      <c r="F32" s="40"/>
       <c r="G32" s="2"/>
       <c r="H32" s="17"/>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="2"/>
-      <c r="B33" s="46" t="s">
+      <c r="B33" s="41" t="s">
         <v>7</v>
       </c>
-      <c r="C33" s="47"/>
-      <c r="D33" s="47"/>
-      <c r="E33" s="47"/>
-      <c r="F33" s="48"/>
+      <c r="C33" s="42"/>
+      <c r="D33" s="42"/>
+      <c r="E33" s="42"/>
+      <c r="F33" s="43"/>
       <c r="G33" s="2"/>
       <c r="H33" s="17"/>
     </row>
@@ -1551,11 +1554,11 @@
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" s="2"/>
-      <c r="B38" s="64"/>
-      <c r="C38" s="65"/>
-      <c r="D38" s="65"/>
-      <c r="E38" s="65"/>
-      <c r="F38" s="66"/>
+      <c r="B38" s="62"/>
+      <c r="C38" s="63"/>
+      <c r="D38" s="63"/>
+      <c r="E38" s="63"/>
+      <c r="F38" s="64"/>
       <c r="G38" s="2"/>
       <c r="H38" s="17"/>
     </row>
@@ -1577,13 +1580,13 @@
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="2"/>
-      <c r="B40" s="29" t="s">
+      <c r="B40" s="47" t="s">
         <v>17</v>
       </c>
-      <c r="C40" s="30"/>
-      <c r="D40" s="30"/>
-      <c r="E40" s="30"/>
-      <c r="F40" s="31"/>
+      <c r="C40" s="48"/>
+      <c r="D40" s="48"/>
+      <c r="E40" s="48"/>
+      <c r="F40" s="49"/>
       <c r="G40" s="2"/>
       <c r="H40" s="17"/>
     </row>
@@ -1625,33 +1628,33 @@
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="2"/>
-      <c r="B44" s="37" t="s">
+      <c r="B44" s="29" t="s">
         <v>21</v>
       </c>
-      <c r="C44" s="38"/>
-      <c r="D44" s="38"/>
-      <c r="E44" s="38"/>
-      <c r="F44" s="39"/>
+      <c r="C44" s="30"/>
+      <c r="D44" s="30"/>
+      <c r="E44" s="30"/>
+      <c r="F44" s="31"/>
       <c r="G44" s="2"/>
       <c r="H44" s="17"/>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" s="2"/>
-      <c r="B45" s="40"/>
-      <c r="C45" s="41"/>
-      <c r="D45" s="41"/>
-      <c r="E45" s="41"/>
-      <c r="F45" s="42"/>
+      <c r="B45" s="32"/>
+      <c r="C45" s="33"/>
+      <c r="D45" s="33"/>
+      <c r="E45" s="33"/>
+      <c r="F45" s="34"/>
       <c r="G45" s="2"/>
       <c r="H45" s="17"/>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" s="2"/>
-      <c r="B46" s="43"/>
-      <c r="C46" s="44"/>
-      <c r="D46" s="44"/>
-      <c r="E46" s="44"/>
-      <c r="F46" s="45"/>
+      <c r="B46" s="35"/>
+      <c r="C46" s="36"/>
+      <c r="D46" s="36"/>
+      <c r="E46" s="36"/>
+      <c r="F46" s="37"/>
       <c r="G46" s="2"/>
       <c r="H46" s="17"/>
     </row>
@@ -1669,15 +1672,15 @@
       <c r="H48" s="17"/>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A49" s="35" t="s">
+      <c r="A49" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="B49" s="36"/>
-      <c r="C49" s="36"/>
-      <c r="D49" s="36"/>
-      <c r="E49" s="36"/>
-      <c r="F49" s="36"/>
-      <c r="G49" s="36"/>
+      <c r="B49" s="39"/>
+      <c r="C49" s="39"/>
+      <c r="D49" s="39"/>
+      <c r="E49" s="39"/>
+      <c r="F49" s="39"/>
+      <c r="G49" s="39"/>
     </row>
     <row r="52" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
@@ -1686,12 +1689,12 @@
       <c r="B52" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C52" s="49" t="s">
+      <c r="C52" s="50" t="s">
         <v>42</v>
       </c>
-      <c r="D52" s="49"/>
-      <c r="E52" s="49"/>
-      <c r="F52" s="49"/>
+      <c r="D52" s="50"/>
+      <c r="E52" s="50"/>
+      <c r="F52" s="50"/>
       <c r="G52" s="2"/>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
@@ -1708,12 +1711,12 @@
       <c r="B54" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="C54" s="50" t="s">
+      <c r="C54" s="51" t="s">
         <v>23</v>
       </c>
-      <c r="D54" s="50"/>
-      <c r="E54" s="50"/>
-      <c r="F54" s="51"/>
+      <c r="D54" s="51"/>
+      <c r="E54" s="51"/>
+      <c r="F54" s="52"/>
       <c r="G54" s="2"/>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
@@ -1721,12 +1724,12 @@
       <c r="B55" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C55" s="52" t="s">
+      <c r="C55" s="40" t="s">
         <v>31</v>
       </c>
-      <c r="D55" s="52"/>
-      <c r="E55" s="52"/>
-      <c r="F55" s="52"/>
+      <c r="D55" s="40"/>
+      <c r="E55" s="40"/>
+      <c r="F55" s="40"/>
       <c r="G55" s="2"/>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
@@ -1734,10 +1737,10 @@
       <c r="B56" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="C56" s="52"/>
-      <c r="D56" s="52"/>
-      <c r="E56" s="52"/>
-      <c r="F56" s="52"/>
+      <c r="C56" s="40"/>
+      <c r="D56" s="40"/>
+      <c r="E56" s="40"/>
+      <c r="F56" s="40"/>
       <c r="G56" s="2"/>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
@@ -1745,23 +1748,23 @@
       <c r="B57" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C57" s="52" t="s">
+      <c r="C57" s="40" t="s">
         <v>43</v>
       </c>
-      <c r="D57" s="52"/>
-      <c r="E57" s="52"/>
-      <c r="F57" s="52"/>
+      <c r="D57" s="40"/>
+      <c r="E57" s="40"/>
+      <c r="F57" s="40"/>
       <c r="G57" s="2"/>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" s="2"/>
-      <c r="B58" s="46" t="s">
+      <c r="B58" s="41" t="s">
         <v>7</v>
       </c>
-      <c r="C58" s="47"/>
-      <c r="D58" s="47"/>
-      <c r="E58" s="47"/>
-      <c r="F58" s="48"/>
+      <c r="C58" s="42"/>
+      <c r="D58" s="42"/>
+      <c r="E58" s="42"/>
+      <c r="F58" s="43"/>
       <c r="G58" s="2"/>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
@@ -1821,11 +1824,11 @@
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" s="2"/>
-      <c r="B62" s="32"/>
-      <c r="C62" s="33"/>
-      <c r="D62" s="33"/>
-      <c r="E62" s="33"/>
-      <c r="F62" s="34"/>
+      <c r="B62" s="44"/>
+      <c r="C62" s="45"/>
+      <c r="D62" s="45"/>
+      <c r="E62" s="45"/>
+      <c r="F62" s="46"/>
       <c r="G62" s="2"/>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
@@ -1845,13 +1848,13 @@
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" s="2"/>
-      <c r="B64" s="29" t="s">
+      <c r="B64" s="47" t="s">
         <v>17</v>
       </c>
-      <c r="C64" s="30"/>
-      <c r="D64" s="30"/>
-      <c r="E64" s="30"/>
-      <c r="F64" s="31"/>
+      <c r="C64" s="48"/>
+      <c r="D64" s="48"/>
+      <c r="E64" s="48"/>
+      <c r="F64" s="49"/>
       <c r="G64" s="2"/>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
@@ -1889,31 +1892,31 @@
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" s="2"/>
-      <c r="B68" s="37" t="s">
+      <c r="B68" s="29" t="s">
         <v>21</v>
       </c>
-      <c r="C68" s="38"/>
-      <c r="D68" s="38"/>
-      <c r="E68" s="38"/>
-      <c r="F68" s="39"/>
+      <c r="C68" s="30"/>
+      <c r="D68" s="30"/>
+      <c r="E68" s="30"/>
+      <c r="F68" s="31"/>
       <c r="G68" s="2"/>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" s="2"/>
-      <c r="B69" s="40"/>
-      <c r="C69" s="41"/>
-      <c r="D69" s="41"/>
-      <c r="E69" s="41"/>
-      <c r="F69" s="42"/>
+      <c r="B69" s="32"/>
+      <c r="C69" s="33"/>
+      <c r="D69" s="33"/>
+      <c r="E69" s="33"/>
+      <c r="F69" s="34"/>
       <c r="G69" s="2"/>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" s="2"/>
-      <c r="B70" s="43"/>
-      <c r="C70" s="44"/>
-      <c r="D70" s="44"/>
-      <c r="E70" s="44"/>
-      <c r="F70" s="45"/>
+      <c r="B70" s="35"/>
+      <c r="C70" s="36"/>
+      <c r="D70" s="36"/>
+      <c r="E70" s="36"/>
+      <c r="F70" s="37"/>
       <c r="G70" s="2"/>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
@@ -1921,15 +1924,15 @@
       <c r="G71" s="2"/>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A73" s="35" t="s">
+      <c r="A73" s="38" t="s">
         <v>44</v>
       </c>
-      <c r="B73" s="36"/>
-      <c r="C73" s="36"/>
-      <c r="D73" s="36"/>
-      <c r="E73" s="36"/>
-      <c r="F73" s="36"/>
-      <c r="G73" s="36"/>
+      <c r="B73" s="39"/>
+      <c r="C73" s="39"/>
+      <c r="D73" s="39"/>
+      <c r="E73" s="39"/>
+      <c r="F73" s="39"/>
+      <c r="G73" s="39"/>
     </row>
     <row r="75" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
@@ -1938,12 +1941,12 @@
       <c r="B75" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="C75" s="49" t="s">
+      <c r="C75" s="50" t="s">
         <v>54</v>
       </c>
-      <c r="D75" s="49"/>
-      <c r="E75" s="49"/>
-      <c r="F75" s="49"/>
+      <c r="D75" s="50"/>
+      <c r="E75" s="50"/>
+      <c r="F75" s="50"/>
       <c r="G75" s="2"/>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
@@ -1960,12 +1963,12 @@
       <c r="B77" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="C77" s="50" t="s">
+      <c r="C77" s="51" t="s">
         <v>23</v>
       </c>
-      <c r="D77" s="50"/>
-      <c r="E77" s="50"/>
-      <c r="F77" s="51"/>
+      <c r="D77" s="51"/>
+      <c r="E77" s="51"/>
+      <c r="F77" s="52"/>
       <c r="G77" s="2"/>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
@@ -1973,12 +1976,12 @@
       <c r="B78" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C78" s="52" t="s">
+      <c r="C78" s="40" t="s">
         <v>31</v>
       </c>
-      <c r="D78" s="52"/>
-      <c r="E78" s="52"/>
-      <c r="F78" s="52"/>
+      <c r="D78" s="40"/>
+      <c r="E78" s="40"/>
+      <c r="F78" s="40"/>
       <c r="G78" s="2"/>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
@@ -1986,10 +1989,10 @@
       <c r="B79" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="C79" s="52"/>
-      <c r="D79" s="52"/>
-      <c r="E79" s="52"/>
-      <c r="F79" s="52"/>
+      <c r="C79" s="40"/>
+      <c r="D79" s="40"/>
+      <c r="E79" s="40"/>
+      <c r="F79" s="40"/>
       <c r="G79" s="2"/>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
@@ -1997,23 +2000,23 @@
       <c r="B80" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C80" s="52" t="s">
+      <c r="C80" s="40" t="s">
         <v>51</v>
       </c>
-      <c r="D80" s="52"/>
-      <c r="E80" s="52"/>
-      <c r="F80" s="52"/>
+      <c r="D80" s="40"/>
+      <c r="E80" s="40"/>
+      <c r="F80" s="40"/>
       <c r="G80" s="2"/>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" s="2"/>
-      <c r="B81" s="46" t="s">
+      <c r="B81" s="41" t="s">
         <v>7</v>
       </c>
-      <c r="C81" s="47"/>
-      <c r="D81" s="47"/>
-      <c r="E81" s="47"/>
-      <c r="F81" s="48"/>
+      <c r="C81" s="42"/>
+      <c r="D81" s="42"/>
+      <c r="E81" s="42"/>
+      <c r="F81" s="43"/>
       <c r="G81" s="2"/>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
@@ -2088,11 +2091,11 @@
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" s="2"/>
-      <c r="B86" s="32"/>
-      <c r="C86" s="33"/>
-      <c r="D86" s="33"/>
-      <c r="E86" s="33"/>
-      <c r="F86" s="34"/>
+      <c r="B86" s="44"/>
+      <c r="C86" s="45"/>
+      <c r="D86" s="45"/>
+      <c r="E86" s="45"/>
+      <c r="F86" s="46"/>
       <c r="G86" s="2"/>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
@@ -2112,13 +2115,13 @@
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88" s="2"/>
-      <c r="B88" s="29" t="s">
+      <c r="B88" s="47" t="s">
         <v>17</v>
       </c>
-      <c r="C88" s="30"/>
-      <c r="D88" s="30"/>
-      <c r="E88" s="30"/>
-      <c r="F88" s="31"/>
+      <c r="C88" s="48"/>
+      <c r="D88" s="48"/>
+      <c r="E88" s="48"/>
+      <c r="F88" s="49"/>
       <c r="G88" s="2"/>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
@@ -2156,31 +2159,31 @@
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92" s="2"/>
-      <c r="B92" s="37" t="s">
+      <c r="B92" s="29" t="s">
         <v>21</v>
       </c>
-      <c r="C92" s="38"/>
-      <c r="D92" s="38"/>
-      <c r="E92" s="38"/>
-      <c r="F92" s="39"/>
+      <c r="C92" s="30"/>
+      <c r="D92" s="30"/>
+      <c r="E92" s="30"/>
+      <c r="F92" s="31"/>
       <c r="G92" s="2"/>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93" s="2"/>
-      <c r="B93" s="40"/>
-      <c r="C93" s="41"/>
-      <c r="D93" s="41"/>
-      <c r="E93" s="41"/>
-      <c r="F93" s="42"/>
+      <c r="B93" s="32"/>
+      <c r="C93" s="33"/>
+      <c r="D93" s="33"/>
+      <c r="E93" s="33"/>
+      <c r="F93" s="34"/>
       <c r="G93" s="2"/>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" s="2"/>
-      <c r="B94" s="43"/>
-      <c r="C94" s="44"/>
-      <c r="D94" s="44"/>
-      <c r="E94" s="44"/>
-      <c r="F94" s="45"/>
+      <c r="B94" s="35"/>
+      <c r="C94" s="36"/>
+      <c r="D94" s="36"/>
+      <c r="E94" s="36"/>
+      <c r="F94" s="37"/>
       <c r="G94" s="2"/>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
@@ -2188,15 +2191,15 @@
       <c r="G95" s="2"/>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A97" s="35" t="s">
+      <c r="A97" s="38" t="s">
         <v>44</v>
       </c>
-      <c r="B97" s="36"/>
-      <c r="C97" s="36"/>
-      <c r="D97" s="36"/>
-      <c r="E97" s="36"/>
-      <c r="F97" s="36"/>
-      <c r="G97" s="36"/>
+      <c r="B97" s="39"/>
+      <c r="C97" s="39"/>
+      <c r="D97" s="39"/>
+      <c r="E97" s="39"/>
+      <c r="F97" s="39"/>
+      <c r="G97" s="39"/>
     </row>
     <row r="99" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
@@ -2205,12 +2208,12 @@
       <c r="B99" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="C99" s="49" t="s">
+      <c r="C99" s="50" t="s">
         <v>61</v>
       </c>
-      <c r="D99" s="49"/>
-      <c r="E99" s="49"/>
-      <c r="F99" s="49"/>
+      <c r="D99" s="50"/>
+      <c r="E99" s="50"/>
+      <c r="F99" s="50"/>
       <c r="G99" s="2"/>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
@@ -2227,12 +2230,12 @@
       <c r="B101" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="C101" s="50" t="s">
+      <c r="C101" s="51" t="s">
         <v>23</v>
       </c>
-      <c r="D101" s="50"/>
-      <c r="E101" s="50"/>
-      <c r="F101" s="51"/>
+      <c r="D101" s="51"/>
+      <c r="E101" s="51"/>
+      <c r="F101" s="52"/>
       <c r="G101" s="2"/>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
@@ -2240,12 +2243,12 @@
       <c r="B102" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C102" s="52" t="s">
+      <c r="C102" s="40" t="s">
         <v>31</v>
       </c>
-      <c r="D102" s="52"/>
-      <c r="E102" s="52"/>
-      <c r="F102" s="52"/>
+      <c r="D102" s="40"/>
+      <c r="E102" s="40"/>
+      <c r="F102" s="40"/>
       <c r="G102" s="2"/>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
@@ -2253,10 +2256,10 @@
       <c r="B103" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="C103" s="52"/>
-      <c r="D103" s="52"/>
-      <c r="E103" s="52"/>
-      <c r="F103" s="52"/>
+      <c r="C103" s="40"/>
+      <c r="D103" s="40"/>
+      <c r="E103" s="40"/>
+      <c r="F103" s="40"/>
       <c r="G103" s="2"/>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
@@ -2264,23 +2267,23 @@
       <c r="B104" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C104" s="52" t="s">
+      <c r="C104" s="40" t="s">
         <v>51</v>
       </c>
-      <c r="D104" s="52"/>
-      <c r="E104" s="52"/>
-      <c r="F104" s="52"/>
+      <c r="D104" s="40"/>
+      <c r="E104" s="40"/>
+      <c r="F104" s="40"/>
       <c r="G104" s="2"/>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105" s="2"/>
-      <c r="B105" s="46" t="s">
+      <c r="B105" s="41" t="s">
         <v>7</v>
       </c>
-      <c r="C105" s="47"/>
-      <c r="D105" s="47"/>
-      <c r="E105" s="47"/>
-      <c r="F105" s="48"/>
+      <c r="C105" s="42"/>
+      <c r="D105" s="42"/>
+      <c r="E105" s="42"/>
+      <c r="F105" s="43"/>
       <c r="G105" s="2"/>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
@@ -2357,11 +2360,11 @@
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A110" s="2"/>
-      <c r="B110" s="32"/>
-      <c r="C110" s="33"/>
-      <c r="D110" s="33"/>
-      <c r="E110" s="33"/>
-      <c r="F110" s="34"/>
+      <c r="B110" s="44"/>
+      <c r="C110" s="45"/>
+      <c r="D110" s="45"/>
+      <c r="E110" s="45"/>
+      <c r="F110" s="46"/>
       <c r="G110" s="2"/>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
@@ -2381,13 +2384,13 @@
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112" s="2"/>
-      <c r="B112" s="29" t="s">
+      <c r="B112" s="47" t="s">
         <v>17</v>
       </c>
-      <c r="C112" s="30"/>
-      <c r="D112" s="30"/>
-      <c r="E112" s="30"/>
-      <c r="F112" s="31"/>
+      <c r="C112" s="48"/>
+      <c r="D112" s="48"/>
+      <c r="E112" s="48"/>
+      <c r="F112" s="49"/>
       <c r="G112" s="2"/>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.25">
@@ -2425,31 +2428,31 @@
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A116" s="2"/>
-      <c r="B116" s="37" t="s">
+      <c r="B116" s="29" t="s">
         <v>21</v>
       </c>
-      <c r="C116" s="38"/>
-      <c r="D116" s="38"/>
-      <c r="E116" s="38"/>
-      <c r="F116" s="39"/>
+      <c r="C116" s="30"/>
+      <c r="D116" s="30"/>
+      <c r="E116" s="30"/>
+      <c r="F116" s="31"/>
       <c r="G116" s="2"/>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A117" s="2"/>
-      <c r="B117" s="40"/>
-      <c r="C117" s="41"/>
-      <c r="D117" s="41"/>
-      <c r="E117" s="41"/>
-      <c r="F117" s="42"/>
+      <c r="B117" s="32"/>
+      <c r="C117" s="33"/>
+      <c r="D117" s="33"/>
+      <c r="E117" s="33"/>
+      <c r="F117" s="34"/>
       <c r="G117" s="2"/>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A118" s="2"/>
-      <c r="B118" s="43"/>
-      <c r="C118" s="44"/>
-      <c r="D118" s="44"/>
-      <c r="E118" s="44"/>
-      <c r="F118" s="45"/>
+      <c r="B118" s="35"/>
+      <c r="C118" s="36"/>
+      <c r="D118" s="36"/>
+      <c r="E118" s="36"/>
+      <c r="F118" s="37"/>
       <c r="G118" s="2"/>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
@@ -2457,15 +2460,15 @@
       <c r="G119" s="2"/>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A121" s="35" t="s">
+      <c r="A121" s="38" t="s">
         <v>44</v>
       </c>
-      <c r="B121" s="36"/>
-      <c r="C121" s="36"/>
-      <c r="D121" s="36"/>
-      <c r="E121" s="36"/>
-      <c r="F121" s="36"/>
-      <c r="G121" s="36"/>
+      <c r="B121" s="39"/>
+      <c r="C121" s="39"/>
+      <c r="D121" s="39"/>
+      <c r="E121" s="39"/>
+      <c r="F121" s="39"/>
+      <c r="G121" s="39"/>
     </row>
     <row r="123" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
@@ -2474,12 +2477,12 @@
       <c r="B123" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="C123" s="49" t="s">
+      <c r="C123" s="50" t="s">
         <v>70</v>
       </c>
-      <c r="D123" s="49"/>
-      <c r="E123" s="49"/>
-      <c r="F123" s="49"/>
+      <c r="D123" s="50"/>
+      <c r="E123" s="50"/>
+      <c r="F123" s="50"/>
       <c r="G123" s="2"/>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.25">
@@ -2496,12 +2499,12 @@
       <c r="B125" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="C125" s="50" t="s">
+      <c r="C125" s="51" t="s">
         <v>23</v>
       </c>
-      <c r="D125" s="50"/>
-      <c r="E125" s="50"/>
-      <c r="F125" s="51"/>
+      <c r="D125" s="51"/>
+      <c r="E125" s="51"/>
+      <c r="F125" s="52"/>
       <c r="G125" s="2"/>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.25">
@@ -2509,12 +2512,12 @@
       <c r="B126" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C126" s="52" t="s">
+      <c r="C126" s="40" t="s">
         <v>31</v>
       </c>
-      <c r="D126" s="52"/>
-      <c r="E126" s="52"/>
-      <c r="F126" s="52"/>
+      <c r="D126" s="40"/>
+      <c r="E126" s="40"/>
+      <c r="F126" s="40"/>
       <c r="G126" s="2"/>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.25">
@@ -2522,10 +2525,10 @@
       <c r="B127" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="C127" s="52"/>
-      <c r="D127" s="52"/>
-      <c r="E127" s="52"/>
-      <c r="F127" s="52"/>
+      <c r="C127" s="40"/>
+      <c r="D127" s="40"/>
+      <c r="E127" s="40"/>
+      <c r="F127" s="40"/>
       <c r="G127" s="2"/>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.25">
@@ -2533,23 +2536,23 @@
       <c r="B128" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C128" s="52" t="s">
-        <v>51</v>
-      </c>
-      <c r="D128" s="52"/>
-      <c r="E128" s="52"/>
-      <c r="F128" s="52"/>
+      <c r="C128" s="40" t="s">
+        <v>85</v>
+      </c>
+      <c r="D128" s="40"/>
+      <c r="E128" s="40"/>
+      <c r="F128" s="40"/>
       <c r="G128" s="2"/>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A129" s="2"/>
-      <c r="B129" s="46" t="s">
+      <c r="B129" s="41" t="s">
         <v>7</v>
       </c>
-      <c r="C129" s="47"/>
-      <c r="D129" s="47"/>
-      <c r="E129" s="47"/>
-      <c r="F129" s="48"/>
+      <c r="C129" s="42"/>
+      <c r="D129" s="42"/>
+      <c r="E129" s="42"/>
+      <c r="F129" s="43"/>
       <c r="G129" s="2"/>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.25">
@@ -2626,11 +2629,11 @@
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A134" s="2"/>
-      <c r="B134" s="32"/>
-      <c r="C134" s="33"/>
-      <c r="D134" s="33"/>
-      <c r="E134" s="33"/>
-      <c r="F134" s="34"/>
+      <c r="B134" s="44"/>
+      <c r="C134" s="45"/>
+      <c r="D134" s="45"/>
+      <c r="E134" s="45"/>
+      <c r="F134" s="46"/>
       <c r="G134" s="2"/>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.25">
@@ -2650,13 +2653,13 @@
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A136" s="2"/>
-      <c r="B136" s="29" t="s">
+      <c r="B136" s="47" t="s">
         <v>17</v>
       </c>
-      <c r="C136" s="30"/>
-      <c r="D136" s="30"/>
-      <c r="E136" s="30"/>
-      <c r="F136" s="31"/>
+      <c r="C136" s="48"/>
+      <c r="D136" s="48"/>
+      <c r="E136" s="48"/>
+      <c r="F136" s="49"/>
       <c r="G136" s="2"/>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.25">
@@ -2694,31 +2697,31 @@
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A140" s="2"/>
-      <c r="B140" s="37" t="s">
+      <c r="B140" s="29" t="s">
         <v>21</v>
       </c>
-      <c r="C140" s="38"/>
-      <c r="D140" s="38"/>
-      <c r="E140" s="38"/>
-      <c r="F140" s="39"/>
+      <c r="C140" s="30"/>
+      <c r="D140" s="30"/>
+      <c r="E140" s="30"/>
+      <c r="F140" s="31"/>
       <c r="G140" s="2"/>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A141" s="2"/>
-      <c r="B141" s="40"/>
-      <c r="C141" s="41"/>
-      <c r="D141" s="41"/>
-      <c r="E141" s="41"/>
-      <c r="F141" s="42"/>
+      <c r="B141" s="32"/>
+      <c r="C141" s="33"/>
+      <c r="D141" s="33"/>
+      <c r="E141" s="33"/>
+      <c r="F141" s="34"/>
       <c r="G141" s="2"/>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A142" s="2"/>
-      <c r="B142" s="43"/>
-      <c r="C142" s="44"/>
-      <c r="D142" s="44"/>
-      <c r="E142" s="44"/>
-      <c r="F142" s="45"/>
+      <c r="B142" s="35"/>
+      <c r="C142" s="36"/>
+      <c r="D142" s="36"/>
+      <c r="E142" s="36"/>
+      <c r="F142" s="37"/>
       <c r="G142" s="2"/>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.25">
@@ -2726,15 +2729,15 @@
       <c r="G143" s="2"/>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A145" s="35" t="s">
+      <c r="A145" s="38" t="s">
         <v>44</v>
       </c>
-      <c r="B145" s="36"/>
-      <c r="C145" s="36"/>
-      <c r="D145" s="36"/>
-      <c r="E145" s="36"/>
-      <c r="F145" s="36"/>
-      <c r="G145" s="36"/>
+      <c r="B145" s="39"/>
+      <c r="C145" s="39"/>
+      <c r="D145" s="39"/>
+      <c r="E145" s="39"/>
+      <c r="F145" s="39"/>
+      <c r="G145" s="39"/>
     </row>
     <row r="147" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
@@ -2743,12 +2746,12 @@
       <c r="B147" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="C147" s="49" t="s">
+      <c r="C147" s="50" t="s">
         <v>78</v>
       </c>
-      <c r="D147" s="49"/>
-      <c r="E147" s="49"/>
-      <c r="F147" s="49"/>
+      <c r="D147" s="50"/>
+      <c r="E147" s="50"/>
+      <c r="F147" s="50"/>
       <c r="G147" s="2"/>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.25">
@@ -2765,12 +2768,12 @@
       <c r="B149" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="C149" s="50" t="s">
+      <c r="C149" s="51" t="s">
         <v>23</v>
       </c>
-      <c r="D149" s="50"/>
-      <c r="E149" s="50"/>
-      <c r="F149" s="51"/>
+      <c r="D149" s="51"/>
+      <c r="E149" s="51"/>
+      <c r="F149" s="52"/>
       <c r="G149" s="2"/>
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.25">
@@ -2778,12 +2781,12 @@
       <c r="B150" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C150" s="52" t="s">
+      <c r="C150" s="40" t="s">
         <v>31</v>
       </c>
-      <c r="D150" s="52"/>
-      <c r="E150" s="52"/>
-      <c r="F150" s="52"/>
+      <c r="D150" s="40"/>
+      <c r="E150" s="40"/>
+      <c r="F150" s="40"/>
       <c r="G150" s="2"/>
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.25">
@@ -2791,10 +2794,10 @@
       <c r="B151" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="C151" s="52"/>
-      <c r="D151" s="52"/>
-      <c r="E151" s="52"/>
-      <c r="F151" s="52"/>
+      <c r="C151" s="40"/>
+      <c r="D151" s="40"/>
+      <c r="E151" s="40"/>
+      <c r="F151" s="40"/>
       <c r="G151" s="2"/>
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.25">
@@ -2802,23 +2805,23 @@
       <c r="B152" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C152" s="52" t="s">
-        <v>51</v>
-      </c>
-      <c r="D152" s="52"/>
-      <c r="E152" s="52"/>
-      <c r="F152" s="52"/>
+      <c r="C152" s="40" t="s">
+        <v>85</v>
+      </c>
+      <c r="D152" s="40"/>
+      <c r="E152" s="40"/>
+      <c r="F152" s="40"/>
       <c r="G152" s="2"/>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A153" s="2"/>
-      <c r="B153" s="46" t="s">
+      <c r="B153" s="41" t="s">
         <v>7</v>
       </c>
-      <c r="C153" s="47"/>
-      <c r="D153" s="47"/>
-      <c r="E153" s="47"/>
-      <c r="F153" s="48"/>
+      <c r="C153" s="42"/>
+      <c r="D153" s="42"/>
+      <c r="E153" s="42"/>
+      <c r="F153" s="43"/>
       <c r="G153" s="2"/>
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.25">
@@ -2914,11 +2917,11 @@
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A159" s="2"/>
-      <c r="B159" s="32"/>
-      <c r="C159" s="33"/>
-      <c r="D159" s="33"/>
-      <c r="E159" s="33"/>
-      <c r="F159" s="34"/>
+      <c r="B159" s="44"/>
+      <c r="C159" s="45"/>
+      <c r="D159" s="45"/>
+      <c r="E159" s="45"/>
+      <c r="F159" s="46"/>
       <c r="G159" s="2"/>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.25">
@@ -2938,13 +2941,13 @@
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A161" s="2"/>
-      <c r="B161" s="29" t="s">
+      <c r="B161" s="47" t="s">
         <v>17</v>
       </c>
-      <c r="C161" s="30"/>
-      <c r="D161" s="30"/>
-      <c r="E161" s="30"/>
-      <c r="F161" s="31"/>
+      <c r="C161" s="48"/>
+      <c r="D161" s="48"/>
+      <c r="E161" s="48"/>
+      <c r="F161" s="49"/>
       <c r="G161" s="2"/>
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.25">
@@ -2982,31 +2985,31 @@
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A165" s="2"/>
-      <c r="B165" s="37" t="s">
+      <c r="B165" s="29" t="s">
         <v>21</v>
       </c>
-      <c r="C165" s="38"/>
-      <c r="D165" s="38"/>
-      <c r="E165" s="38"/>
-      <c r="F165" s="39"/>
+      <c r="C165" s="30"/>
+      <c r="D165" s="30"/>
+      <c r="E165" s="30"/>
+      <c r="F165" s="31"/>
       <c r="G165" s="2"/>
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A166" s="2"/>
-      <c r="B166" s="40"/>
-      <c r="C166" s="41"/>
-      <c r="D166" s="41"/>
-      <c r="E166" s="41"/>
-      <c r="F166" s="42"/>
+      <c r="B166" s="32"/>
+      <c r="C166" s="33"/>
+      <c r="D166" s="33"/>
+      <c r="E166" s="33"/>
+      <c r="F166" s="34"/>
       <c r="G166" s="2"/>
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A167" s="2"/>
-      <c r="B167" s="43"/>
-      <c r="C167" s="44"/>
-      <c r="D167" s="44"/>
-      <c r="E167" s="44"/>
-      <c r="F167" s="45"/>
+      <c r="B167" s="35"/>
+      <c r="C167" s="36"/>
+      <c r="D167" s="36"/>
+      <c r="E167" s="36"/>
+      <c r="F167" s="37"/>
       <c r="G167" s="2"/>
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.25">
@@ -3014,43 +3017,70 @@
       <c r="G168" s="2"/>
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A170" s="35" t="s">
+      <c r="A170" s="38" t="s">
         <v>44</v>
       </c>
-      <c r="B170" s="36"/>
-      <c r="C170" s="36"/>
-      <c r="D170" s="36"/>
-      <c r="E170" s="36"/>
-      <c r="F170" s="36"/>
-      <c r="G170" s="36"/>
+      <c r="B170" s="39"/>
+      <c r="C170" s="39"/>
+      <c r="D170" s="39"/>
+      <c r="E170" s="39"/>
+      <c r="F170" s="39"/>
+      <c r="G170" s="39"/>
     </row>
   </sheetData>
   <mergeCells count="93">
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B163:F163"/>
-    <mergeCell ref="B164:F164"/>
-    <mergeCell ref="B165:F167"/>
-    <mergeCell ref="A170:G170"/>
-    <mergeCell ref="C151:F151"/>
-    <mergeCell ref="C152:F152"/>
-    <mergeCell ref="B153:F153"/>
-    <mergeCell ref="B159:F159"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B140:F142"/>
-    <mergeCell ref="A145:G145"/>
-    <mergeCell ref="C147:F147"/>
-    <mergeCell ref="C149:F149"/>
-    <mergeCell ref="C150:F150"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B136:F136"/>
-    <mergeCell ref="B137:F137"/>
-    <mergeCell ref="B138:F138"/>
-    <mergeCell ref="B139:F139"/>
-    <mergeCell ref="C125:F125"/>
-    <mergeCell ref="C126:F126"/>
-    <mergeCell ref="C127:F127"/>
-    <mergeCell ref="C128:F128"/>
-    <mergeCell ref="B129:F129"/>
+    <mergeCell ref="A73:G73"/>
+    <mergeCell ref="B68:F70"/>
+    <mergeCell ref="B58:F58"/>
+    <mergeCell ref="C52:F52"/>
+    <mergeCell ref="C54:F54"/>
+    <mergeCell ref="C55:F55"/>
+    <mergeCell ref="C56:F56"/>
+    <mergeCell ref="C57:F57"/>
+    <mergeCell ref="B65:F65"/>
+    <mergeCell ref="B66:F66"/>
+    <mergeCell ref="B67:F67"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B62:F62"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="C3:E3"/>
+    <mergeCell ref="C7:F7"/>
+    <mergeCell ref="C8:F8"/>
+    <mergeCell ref="C9:F9"/>
+    <mergeCell ref="C10:F10"/>
+    <mergeCell ref="C32:F32"/>
+    <mergeCell ref="A49:G49"/>
+    <mergeCell ref="B14:F14"/>
+    <mergeCell ref="B17:F17"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B19:F19"/>
+    <mergeCell ref="B20:F22"/>
+    <mergeCell ref="B16:F16"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B38:F38"/>
+    <mergeCell ref="A26:G26"/>
+    <mergeCell ref="A24:G24"/>
+    <mergeCell ref="C27:F27"/>
+    <mergeCell ref="C29:F29"/>
+    <mergeCell ref="C30:F30"/>
+    <mergeCell ref="C31:F31"/>
+    <mergeCell ref="B44:F46"/>
+    <mergeCell ref="B41:F41"/>
+    <mergeCell ref="B42:F42"/>
+    <mergeCell ref="B43:F43"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="C99:F99"/>
+    <mergeCell ref="C101:F101"/>
+    <mergeCell ref="C102:F102"/>
+    <mergeCell ref="C103:F103"/>
+    <mergeCell ref="C104:F104"/>
+    <mergeCell ref="A121:G121"/>
+    <mergeCell ref="B105:F105"/>
+    <mergeCell ref="B110:F110"/>
+    <mergeCell ref="B112:F112"/>
+    <mergeCell ref="B113:F113"/>
+    <mergeCell ref="B114:F114"/>
     <mergeCell ref="C123:F123"/>
     <mergeCell ref="A97:G97"/>
     <mergeCell ref="C75:F75"/>
@@ -3067,58 +3097,31 @@
     <mergeCell ref="C78:F78"/>
     <mergeCell ref="B115:F115"/>
     <mergeCell ref="B116:F118"/>
-    <mergeCell ref="A121:G121"/>
-    <mergeCell ref="B105:F105"/>
-    <mergeCell ref="B110:F110"/>
-    <mergeCell ref="B112:F112"/>
-    <mergeCell ref="B113:F113"/>
-    <mergeCell ref="B114:F114"/>
-    <mergeCell ref="C99:F99"/>
-    <mergeCell ref="C101:F101"/>
-    <mergeCell ref="C102:F102"/>
-    <mergeCell ref="C103:F103"/>
-    <mergeCell ref="C104:F104"/>
-    <mergeCell ref="B44:F46"/>
-    <mergeCell ref="B41:F41"/>
-    <mergeCell ref="B42:F42"/>
-    <mergeCell ref="B43:F43"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="C32:F32"/>
-    <mergeCell ref="A49:G49"/>
-    <mergeCell ref="B14:F14"/>
-    <mergeCell ref="B17:F17"/>
-    <mergeCell ref="B18:F18"/>
-    <mergeCell ref="B19:F19"/>
-    <mergeCell ref="B20:F22"/>
-    <mergeCell ref="B16:F16"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B38:F38"/>
-    <mergeCell ref="A26:G26"/>
-    <mergeCell ref="A24:G24"/>
-    <mergeCell ref="C27:F27"/>
-    <mergeCell ref="C29:F29"/>
-    <mergeCell ref="C30:F30"/>
-    <mergeCell ref="C31:F31"/>
-    <mergeCell ref="B11:F11"/>
-    <mergeCell ref="C1:E1"/>
-    <mergeCell ref="C3:E3"/>
-    <mergeCell ref="C7:F7"/>
-    <mergeCell ref="C8:F8"/>
-    <mergeCell ref="C9:F9"/>
-    <mergeCell ref="C10:F10"/>
-    <mergeCell ref="A73:G73"/>
-    <mergeCell ref="B68:F70"/>
-    <mergeCell ref="B58:F58"/>
-    <mergeCell ref="C52:F52"/>
-    <mergeCell ref="C54:F54"/>
-    <mergeCell ref="C55:F55"/>
-    <mergeCell ref="C56:F56"/>
-    <mergeCell ref="C57:F57"/>
-    <mergeCell ref="B65:F65"/>
-    <mergeCell ref="B66:F66"/>
-    <mergeCell ref="B67:F67"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B62:F62"/>
+    <mergeCell ref="C125:F125"/>
+    <mergeCell ref="C126:F126"/>
+    <mergeCell ref="C127:F127"/>
+    <mergeCell ref="C128:F128"/>
+    <mergeCell ref="B129:F129"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B136:F136"/>
+    <mergeCell ref="B137:F137"/>
+    <mergeCell ref="B138:F138"/>
+    <mergeCell ref="B139:F139"/>
+    <mergeCell ref="B140:F142"/>
+    <mergeCell ref="A145:G145"/>
+    <mergeCell ref="C147:F147"/>
+    <mergeCell ref="C149:F149"/>
+    <mergeCell ref="C150:F150"/>
+    <mergeCell ref="C151:F151"/>
+    <mergeCell ref="C152:F152"/>
+    <mergeCell ref="B153:F153"/>
+    <mergeCell ref="B159:F159"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B163:F163"/>
+    <mergeCell ref="B164:F164"/>
+    <mergeCell ref="B165:F167"/>
+    <mergeCell ref="A170:G170"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Plannification/Fiche_recette_LaDiscorde.xlsx
+++ b/Plannification/Fiche_recette_LaDiscorde.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\matisse.begaud\Documents\GitHub\mini_projet2\Plannification\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bonna\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFCBEE21-41E3-465F-8991-8D9462928014}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E7F41B1-B098-471B-8445-EB3CA8F19B2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F0C29018-6AE5-422C-A279-19C0BD496EEE}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{F0C29018-6AE5-422C-A279-19C0BD496EEE}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="92">
   <si>
     <t>Fiche recettes</t>
   </si>
@@ -136,9 +136,6 @@
     <t>Démarrer la BDD</t>
   </si>
   <si>
-    <t>La base de données ce lance</t>
-  </si>
-  <si>
     <t>Avoir créé la BDD</t>
   </si>
   <si>
@@ -154,27 +151,12 @@
     <t>Lancer le serveur</t>
   </si>
   <si>
-    <t>Avoir lancer la BDD / Avoir installer node</t>
-  </si>
-  <si>
     <t>Aller dans le dossier serveur du projet</t>
   </si>
   <si>
     <t>Vous êtes dans le dossier Serveur</t>
   </si>
   <si>
-    <t>Cliquer sur la barre de naviguation de l'explorateur de fichier et noter "cmd"</t>
-  </si>
-  <si>
-    <t>l'inviter de commande ce lance dans avec le bon chemin</t>
-  </si>
-  <si>
-    <t>Utiliser la commande "node server.js"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Le serveur ce lance </t>
-  </si>
-  <si>
     <t xml:space="preserve"> 2/x</t>
   </si>
   <si>
@@ -184,30 +166,15 @@
     <t>Scénario 3.</t>
   </si>
   <si>
-    <t>Connexion à la page web</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Avoir lancé la BDD / Avoir lancé le serveur </t>
-  </si>
-  <si>
     <t xml:space="preserve"> 3/x</t>
   </si>
   <si>
-    <t>Laner un navigateur web</t>
-  </si>
-  <si>
-    <t>Le navigateur ce lance</t>
-  </si>
-  <si>
     <t>Cliquer sur la barre de navigation du navigateur et entrer l'hostname du serveur</t>
   </si>
   <si>
     <t>C206-03:3000/login.html</t>
   </si>
   <si>
-    <t>vous arrivez sur le menu de connexion de LaDiscorde</t>
-  </si>
-  <si>
     <t>Scénario 4.</t>
   </si>
   <si>
@@ -314,6 +281,57 @@
   </si>
   <si>
     <t>Avoir lancé la BDD / Avoir lancé le serveur / être connecter a la page/s'être authentifié</t>
+  </si>
+  <si>
+    <t>La base de données se lance</t>
+  </si>
+  <si>
+    <t>Élements à tester</t>
+  </si>
+  <si>
+    <t>Pré-requis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Testé par : </t>
+  </si>
+  <si>
+    <t>Avoir lancé la BDD / Avoir installé node</t>
+  </si>
+  <si>
+    <t>Cliquer sur la barre de navigation de l'explorateur de fichier et noter "cmd"</t>
+  </si>
+  <si>
+    <t>l'invite de commande se lance dans l'explorateur de fichier avec le bon chemin</t>
+  </si>
+  <si>
+    <t>Taper la commande "node server.js"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le serveur se lance </t>
+  </si>
+  <si>
+    <t>Lancer un navigateur web</t>
+  </si>
+  <si>
+    <t>Le navigateur se lance</t>
+  </si>
+  <si>
+    <t>Se connecter au menu principal</t>
+  </si>
+  <si>
+    <t>Connexion au site Internet</t>
+  </si>
+  <si>
+    <t>Avoir lancé le serveur sur la machine de test</t>
+  </si>
+  <si>
+    <t>Vous arrivez sur le menu de connexion de LaDiscorde</t>
+  </si>
+  <si>
+    <t>Vérifier le mail lors de la création de compte</t>
+  </si>
+  <si>
+    <t>S'être connecté au site Internet</t>
   </si>
 </sst>
 </file>
@@ -620,6 +638,60 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -647,50 +719,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -701,23 +737,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -754,12 +778,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1111,13 +1129,13 @@
         <v>24</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C1" s="65" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1" s="53" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="65"/>
-      <c r="E1" s="65"/>
+      <c r="D1" s="53"/>
+      <c r="E1" s="53"/>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
     </row>
@@ -1135,11 +1153,11 @@
       <c r="B3" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="50" t="s">
+      <c r="C3" s="34" t="s">
         <v>25</v>
       </c>
-      <c r="D3" s="50"/>
-      <c r="E3" s="50"/>
+      <c r="D3" s="34"/>
+      <c r="E3" s="34"/>
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
     </row>
@@ -1175,12 +1193,12 @@
       <c r="B7" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="51" t="s">
+      <c r="C7" s="35" t="s">
         <v>3</v>
       </c>
-      <c r="D7" s="51"/>
-      <c r="E7" s="51"/>
-      <c r="F7" s="52"/>
+      <c r="D7" s="35"/>
+      <c r="E7" s="35"/>
+      <c r="F7" s="36"/>
       <c r="G7" s="2"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -1188,47 +1206,47 @@
       <c r="B8" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="66" t="s">
-        <v>26</v>
-      </c>
-      <c r="D8" s="66"/>
-      <c r="E8" s="66"/>
-      <c r="F8" s="66"/>
+      <c r="C8" s="54" t="s">
+        <v>75</v>
+      </c>
+      <c r="D8" s="54"/>
+      <c r="E8" s="54"/>
+      <c r="F8" s="54"/>
       <c r="G8" s="2"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="2"/>
       <c r="B9" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="C9" s="66"/>
-      <c r="D9" s="66"/>
-      <c r="E9" s="66"/>
-      <c r="F9" s="66"/>
+        <v>76</v>
+      </c>
+      <c r="C9" s="54"/>
+      <c r="D9" s="54"/>
+      <c r="E9" s="54"/>
+      <c r="F9" s="54"/>
       <c r="G9" s="2"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="2"/>
       <c r="B10" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C10" s="66" t="s">
-        <v>27</v>
-      </c>
-      <c r="D10" s="66"/>
-      <c r="E10" s="66"/>
-      <c r="F10" s="66"/>
+        <v>77</v>
+      </c>
+      <c r="C10" s="54" t="s">
+        <v>26</v>
+      </c>
+      <c r="D10" s="54"/>
+      <c r="E10" s="54"/>
+      <c r="F10" s="54"/>
       <c r="G10" s="2"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="2"/>
-      <c r="B11" s="41" t="s">
+      <c r="B11" s="31" t="s">
         <v>7</v>
       </c>
-      <c r="C11" s="42"/>
-      <c r="D11" s="42"/>
-      <c r="E11" s="42"/>
-      <c r="F11" s="43"/>
+      <c r="C11" s="32"/>
+      <c r="D11" s="32"/>
+      <c r="E11" s="32"/>
+      <c r="F11" s="33"/>
       <c r="G11" s="2"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -1256,11 +1274,11 @@
         <v>1</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D13" s="5"/>
       <c r="E13" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F13" s="5" t="s">
         <v>13</v>
@@ -1269,11 +1287,11 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="2"/>
-      <c r="B14" s="53"/>
-      <c r="C14" s="54"/>
-      <c r="D14" s="54"/>
-      <c r="E14" s="54"/>
-      <c r="F14" s="55"/>
+      <c r="B14" s="55"/>
+      <c r="C14" s="56"/>
+      <c r="D14" s="56"/>
+      <c r="E14" s="56"/>
+      <c r="F14" s="57"/>
       <c r="G14" s="2"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -1282,7 +1300,7 @@
         <v>14</v>
       </c>
       <c r="C15" s="18" t="s">
-        <v>15</v>
+        <v>78</v>
       </c>
       <c r="D15" s="19"/>
       <c r="E15" s="18" t="s">
@@ -1293,75 +1311,75 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="2"/>
-      <c r="B16" s="59" t="s">
+      <c r="B16" s="61" t="s">
         <v>17</v>
       </c>
-      <c r="C16" s="60"/>
-      <c r="D16" s="60"/>
-      <c r="E16" s="60"/>
-      <c r="F16" s="61"/>
+      <c r="C16" s="62"/>
+      <c r="D16" s="62"/>
+      <c r="E16" s="62"/>
+      <c r="F16" s="63"/>
       <c r="G16" s="2"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="2"/>
-      <c r="B17" s="56" t="s">
+      <c r="B17" s="58" t="s">
         <v>18</v>
       </c>
-      <c r="C17" s="57"/>
-      <c r="D17" s="57"/>
-      <c r="E17" s="57"/>
-      <c r="F17" s="58"/>
+      <c r="C17" s="59"/>
+      <c r="D17" s="59"/>
+      <c r="E17" s="59"/>
+      <c r="F17" s="60"/>
       <c r="G17" s="2"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
-      <c r="B18" s="23" t="s">
+      <c r="B18" s="41" t="s">
         <v>19</v>
       </c>
-      <c r="C18" s="24"/>
-      <c r="D18" s="24"/>
-      <c r="E18" s="24"/>
-      <c r="F18" s="25"/>
+      <c r="C18" s="42"/>
+      <c r="D18" s="42"/>
+      <c r="E18" s="42"/>
+      <c r="F18" s="43"/>
       <c r="G18" s="2"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="2"/>
-      <c r="B19" s="26" t="s">
+      <c r="B19" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="C19" s="27"/>
-      <c r="D19" s="27"/>
-      <c r="E19" s="27"/>
-      <c r="F19" s="28"/>
+      <c r="C19" s="45"/>
+      <c r="D19" s="45"/>
+      <c r="E19" s="45"/>
+      <c r="F19" s="46"/>
       <c r="G19" s="2"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="2"/>
-      <c r="B20" s="29" t="s">
+      <c r="B20" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="C20" s="30"/>
-      <c r="D20" s="30"/>
-      <c r="E20" s="30"/>
-      <c r="F20" s="31"/>
+      <c r="C20" s="23"/>
+      <c r="D20" s="23"/>
+      <c r="E20" s="23"/>
+      <c r="F20" s="24"/>
       <c r="G20" s="2"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="2"/>
-      <c r="B21" s="32"/>
-      <c r="C21" s="33"/>
-      <c r="D21" s="33"/>
-      <c r="E21" s="33"/>
-      <c r="F21" s="34"/>
+      <c r="B21" s="25"/>
+      <c r="C21" s="26"/>
+      <c r="D21" s="26"/>
+      <c r="E21" s="26"/>
+      <c r="F21" s="27"/>
       <c r="G21" s="2"/>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="2"/>
-      <c r="B22" s="35"/>
-      <c r="C22" s="36"/>
-      <c r="D22" s="36"/>
-      <c r="E22" s="36"/>
-      <c r="F22" s="37"/>
+      <c r="B22" s="28"/>
+      <c r="C22" s="29"/>
+      <c r="D22" s="29"/>
+      <c r="E22" s="29"/>
+      <c r="F22" s="30"/>
       <c r="G22" s="2"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
@@ -1369,38 +1387,38 @@
       <c r="G23" s="2"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="38" t="s">
-        <v>40</v>
-      </c>
-      <c r="B24" s="39"/>
-      <c r="C24" s="39"/>
-      <c r="D24" s="39"/>
-      <c r="E24" s="39"/>
-      <c r="F24" s="39"/>
-      <c r="G24" s="39"/>
+      <c r="A24" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="B24" s="21"/>
+      <c r="C24" s="21"/>
+      <c r="D24" s="21"/>
+      <c r="E24" s="21"/>
+      <c r="F24" s="21"/>
+      <c r="G24" s="21"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="38"/>
-      <c r="B26" s="39"/>
-      <c r="C26" s="39"/>
-      <c r="D26" s="39"/>
-      <c r="E26" s="39"/>
-      <c r="F26" s="39"/>
-      <c r="G26" s="39"/>
+      <c r="A26" s="20"/>
+      <c r="B26" s="21"/>
+      <c r="C26" s="21"/>
+      <c r="D26" s="21"/>
+      <c r="E26" s="21"/>
+      <c r="F26" s="21"/>
+      <c r="G26" s="21"/>
     </row>
     <row r="27" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C27" s="50" t="s">
-        <v>31</v>
-      </c>
-      <c r="D27" s="50"/>
-      <c r="E27" s="50"/>
-      <c r="F27" s="50"/>
+      <c r="C27" s="34" t="s">
+        <v>30</v>
+      </c>
+      <c r="D27" s="34"/>
+      <c r="E27" s="34"/>
+      <c r="F27" s="34"/>
       <c r="G27" s="2"/>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
@@ -1417,12 +1435,12 @@
       <c r="B29" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="C29" s="51" t="s">
+      <c r="C29" s="35" t="s">
         <v>23</v>
       </c>
-      <c r="D29" s="51"/>
-      <c r="E29" s="51"/>
-      <c r="F29" s="52"/>
+      <c r="D29" s="35"/>
+      <c r="E29" s="35"/>
+      <c r="F29" s="36"/>
       <c r="G29" s="2"/>
       <c r="H29" s="17"/>
     </row>
@@ -1431,12 +1449,12 @@
       <c r="B30" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C30" s="40" t="s">
-        <v>31</v>
-      </c>
-      <c r="D30" s="40"/>
-      <c r="E30" s="40"/>
-      <c r="F30" s="40"/>
+      <c r="C30" s="37" t="s">
+        <v>30</v>
+      </c>
+      <c r="D30" s="37"/>
+      <c r="E30" s="37"/>
+      <c r="F30" s="37"/>
       <c r="G30" s="2"/>
       <c r="H30" s="17"/>
     </row>
@@ -1445,36 +1463,36 @@
       <c r="B31" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="C31" s="40"/>
-      <c r="D31" s="40"/>
-      <c r="E31" s="40"/>
-      <c r="F31" s="40"/>
+      <c r="C31" s="37"/>
+      <c r="D31" s="37"/>
+      <c r="E31" s="37"/>
+      <c r="F31" s="37"/>
       <c r="G31" s="2"/>
       <c r="H31" s="17"/>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="2"/>
       <c r="B32" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C32" s="40" t="s">
-        <v>32</v>
-      </c>
-      <c r="D32" s="40"/>
-      <c r="E32" s="40"/>
-      <c r="F32" s="40"/>
+        <v>77</v>
+      </c>
+      <c r="C32" s="37" t="s">
+        <v>79</v>
+      </c>
+      <c r="D32" s="37"/>
+      <c r="E32" s="37"/>
+      <c r="F32" s="37"/>
       <c r="G32" s="2"/>
       <c r="H32" s="17"/>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="2"/>
-      <c r="B33" s="41" t="s">
+      <c r="B33" s="31" t="s">
         <v>7</v>
       </c>
-      <c r="C33" s="42"/>
-      <c r="D33" s="42"/>
-      <c r="E33" s="42"/>
-      <c r="F33" s="43"/>
+      <c r="C33" s="32"/>
+      <c r="D33" s="32"/>
+      <c r="E33" s="32"/>
+      <c r="F33" s="33"/>
       <c r="G33" s="2"/>
       <c r="H33" s="17"/>
     </row>
@@ -1504,11 +1522,11 @@
         <v>1</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D35" s="5"/>
       <c r="E35" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F35" s="5" t="s">
         <v>13</v>
@@ -1522,11 +1540,11 @@
         <v>2</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>35</v>
+        <v>80</v>
       </c>
       <c r="D36" s="8"/>
       <c r="E36" s="9" t="s">
-        <v>36</v>
+        <v>81</v>
       </c>
       <c r="F36" s="8" t="s">
         <v>13</v>
@@ -1534,17 +1552,17 @@
       <c r="G36" s="2"/>
       <c r="H36" s="17"/>
     </row>
-    <row r="37" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A37" s="2"/>
       <c r="B37" s="7">
         <v>3</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>37</v>
+        <v>82</v>
       </c>
       <c r="D37" s="7"/>
       <c r="E37" s="7" t="s">
-        <v>38</v>
+        <v>83</v>
       </c>
       <c r="F37" s="7" t="s">
         <v>13</v>
@@ -1554,11 +1572,11 @@
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" s="2"/>
-      <c r="B38" s="62"/>
-      <c r="C38" s="63"/>
-      <c r="D38" s="63"/>
-      <c r="E38" s="63"/>
-      <c r="F38" s="64"/>
+      <c r="B38" s="64"/>
+      <c r="C38" s="65"/>
+      <c r="D38" s="65"/>
+      <c r="E38" s="65"/>
+      <c r="F38" s="66"/>
       <c r="G38" s="2"/>
       <c r="H38" s="17"/>
     </row>
@@ -1568,7 +1586,7 @@
         <v>14</v>
       </c>
       <c r="C39" s="16" t="s">
-        <v>15</v>
+        <v>78</v>
       </c>
       <c r="D39" s="14"/>
       <c r="E39" s="16" t="s">
@@ -1592,69 +1610,69 @@
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="2"/>
-      <c r="B41" s="20" t="s">
+      <c r="B41" s="38" t="s">
         <v>18</v>
       </c>
-      <c r="C41" s="21"/>
-      <c r="D41" s="21"/>
-      <c r="E41" s="21"/>
-      <c r="F41" s="22"/>
+      <c r="C41" s="39"/>
+      <c r="D41" s="39"/>
+      <c r="E41" s="39"/>
+      <c r="F41" s="40"/>
       <c r="G41" s="2"/>
       <c r="H41" s="17"/>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="2"/>
-      <c r="B42" s="23" t="s">
+      <c r="B42" s="41" t="s">
         <v>19</v>
       </c>
-      <c r="C42" s="24"/>
-      <c r="D42" s="24"/>
-      <c r="E42" s="24"/>
-      <c r="F42" s="25"/>
+      <c r="C42" s="42"/>
+      <c r="D42" s="42"/>
+      <c r="E42" s="42"/>
+      <c r="F42" s="43"/>
       <c r="G42" s="2"/>
       <c r="H42" s="17"/>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="2"/>
-      <c r="B43" s="26" t="s">
+      <c r="B43" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="C43" s="27"/>
-      <c r="D43" s="27"/>
-      <c r="E43" s="27"/>
-      <c r="F43" s="28"/>
+      <c r="C43" s="45"/>
+      <c r="D43" s="45"/>
+      <c r="E43" s="45"/>
+      <c r="F43" s="46"/>
       <c r="G43" s="2"/>
       <c r="H43" s="17"/>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="2"/>
-      <c r="B44" s="29" t="s">
+      <c r="B44" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="C44" s="30"/>
-      <c r="D44" s="30"/>
-      <c r="E44" s="30"/>
-      <c r="F44" s="31"/>
+      <c r="C44" s="23"/>
+      <c r="D44" s="23"/>
+      <c r="E44" s="23"/>
+      <c r="F44" s="24"/>
       <c r="G44" s="2"/>
       <c r="H44" s="17"/>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" s="2"/>
-      <c r="B45" s="32"/>
-      <c r="C45" s="33"/>
-      <c r="D45" s="33"/>
-      <c r="E45" s="33"/>
-      <c r="F45" s="34"/>
+      <c r="B45" s="25"/>
+      <c r="C45" s="26"/>
+      <c r="D45" s="26"/>
+      <c r="E45" s="26"/>
+      <c r="F45" s="27"/>
       <c r="G45" s="2"/>
       <c r="H45" s="17"/>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" s="2"/>
-      <c r="B46" s="35"/>
-      <c r="C46" s="36"/>
-      <c r="D46" s="36"/>
-      <c r="E46" s="36"/>
-      <c r="F46" s="37"/>
+      <c r="B46" s="28"/>
+      <c r="C46" s="29"/>
+      <c r="D46" s="29"/>
+      <c r="E46" s="29"/>
+      <c r="F46" s="30"/>
       <c r="G46" s="2"/>
       <c r="H46" s="17"/>
     </row>
@@ -1672,29 +1690,29 @@
       <c r="H48" s="17"/>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A49" s="38" t="s">
-        <v>39</v>
-      </c>
-      <c r="B49" s="39"/>
-      <c r="C49" s="39"/>
-      <c r="D49" s="39"/>
-      <c r="E49" s="39"/>
-      <c r="F49" s="39"/>
-      <c r="G49" s="39"/>
+      <c r="A49" s="20" t="s">
+        <v>33</v>
+      </c>
+      <c r="B49" s="21"/>
+      <c r="C49" s="21"/>
+      <c r="D49" s="21"/>
+      <c r="E49" s="21"/>
+      <c r="F49" s="21"/>
+      <c r="G49" s="21"/>
     </row>
     <row r="52" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="C52" s="50" t="s">
-        <v>42</v>
-      </c>
-      <c r="D52" s="50"/>
-      <c r="E52" s="50"/>
-      <c r="F52" s="50"/>
+        <v>35</v>
+      </c>
+      <c r="C52" s="34" t="s">
+        <v>87</v>
+      </c>
+      <c r="D52" s="34"/>
+      <c r="E52" s="34"/>
+      <c r="F52" s="34"/>
       <c r="G52" s="2"/>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
@@ -1711,12 +1729,12 @@
       <c r="B54" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="C54" s="51" t="s">
+      <c r="C54" s="35" t="s">
         <v>23</v>
       </c>
-      <c r="D54" s="51"/>
-      <c r="E54" s="51"/>
-      <c r="F54" s="52"/>
+      <c r="D54" s="35"/>
+      <c r="E54" s="35"/>
+      <c r="F54" s="36"/>
       <c r="G54" s="2"/>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
@@ -1724,12 +1742,12 @@
       <c r="B55" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C55" s="40" t="s">
-        <v>31</v>
-      </c>
-      <c r="D55" s="40"/>
-      <c r="E55" s="40"/>
-      <c r="F55" s="40"/>
+      <c r="C55" s="37" t="s">
+        <v>86</v>
+      </c>
+      <c r="D55" s="37"/>
+      <c r="E55" s="37"/>
+      <c r="F55" s="37"/>
       <c r="G55" s="2"/>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
@@ -1737,34 +1755,34 @@
       <c r="B56" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="C56" s="40"/>
-      <c r="D56" s="40"/>
-      <c r="E56" s="40"/>
-      <c r="F56" s="40"/>
+      <c r="C56" s="37"/>
+      <c r="D56" s="37"/>
+      <c r="E56" s="37"/>
+      <c r="F56" s="37"/>
       <c r="G56" s="2"/>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" s="2"/>
       <c r="B57" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C57" s="40" t="s">
-        <v>43</v>
-      </c>
-      <c r="D57" s="40"/>
-      <c r="E57" s="40"/>
-      <c r="F57" s="40"/>
+        <v>77</v>
+      </c>
+      <c r="C57" s="37" t="s">
+        <v>88</v>
+      </c>
+      <c r="D57" s="37"/>
+      <c r="E57" s="37"/>
+      <c r="F57" s="37"/>
       <c r="G57" s="2"/>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" s="2"/>
-      <c r="B58" s="41" t="s">
+      <c r="B58" s="31" t="s">
         <v>7</v>
       </c>
-      <c r="C58" s="42"/>
-      <c r="D58" s="42"/>
-      <c r="E58" s="42"/>
-      <c r="F58" s="43"/>
+      <c r="C58" s="32"/>
+      <c r="D58" s="32"/>
+      <c r="E58" s="32"/>
+      <c r="F58" s="33"/>
       <c r="G58" s="2"/>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
@@ -1792,11 +1810,11 @@
         <v>1</v>
       </c>
       <c r="C60" s="7" t="s">
-        <v>45</v>
+        <v>84</v>
       </c>
       <c r="D60" s="5"/>
       <c r="E60" s="7" t="s">
-        <v>46</v>
+        <v>85</v>
       </c>
       <c r="F60" s="5" t="s">
         <v>13</v>
@@ -1809,13 +1827,13 @@
         <v>2</v>
       </c>
       <c r="C61" s="9" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="D61" s="9" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>49</v>
+        <v>89</v>
       </c>
       <c r="F61" s="8" t="s">
         <v>13</v>
@@ -1824,11 +1842,11 @@
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" s="2"/>
-      <c r="B62" s="44"/>
-      <c r="C62" s="45"/>
-      <c r="D62" s="45"/>
-      <c r="E62" s="45"/>
-      <c r="F62" s="46"/>
+      <c r="B62" s="50"/>
+      <c r="C62" s="51"/>
+      <c r="D62" s="51"/>
+      <c r="E62" s="51"/>
+      <c r="F62" s="52"/>
       <c r="G62" s="2"/>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
@@ -1837,7 +1855,7 @@
         <v>14</v>
       </c>
       <c r="C63" s="18" t="s">
-        <v>15</v>
+        <v>78</v>
       </c>
       <c r="D63" s="19"/>
       <c r="E63" s="18" t="s">
@@ -1859,64 +1877,64 @@
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" s="2"/>
-      <c r="B65" s="20" t="s">
+      <c r="B65" s="38" t="s">
         <v>18</v>
       </c>
-      <c r="C65" s="21"/>
-      <c r="D65" s="21"/>
-      <c r="E65" s="21"/>
-      <c r="F65" s="22"/>
+      <c r="C65" s="39"/>
+      <c r="D65" s="39"/>
+      <c r="E65" s="39"/>
+      <c r="F65" s="40"/>
       <c r="G65" s="2"/>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" s="2"/>
-      <c r="B66" s="23" t="s">
+      <c r="B66" s="41" t="s">
         <v>19</v>
       </c>
-      <c r="C66" s="24"/>
-      <c r="D66" s="24"/>
-      <c r="E66" s="24"/>
-      <c r="F66" s="25"/>
+      <c r="C66" s="42"/>
+      <c r="D66" s="42"/>
+      <c r="E66" s="42"/>
+      <c r="F66" s="43"/>
       <c r="G66" s="2"/>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" s="2"/>
-      <c r="B67" s="26" t="s">
+      <c r="B67" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="C67" s="27"/>
-      <c r="D67" s="27"/>
-      <c r="E67" s="27"/>
-      <c r="F67" s="28"/>
+      <c r="C67" s="45"/>
+      <c r="D67" s="45"/>
+      <c r="E67" s="45"/>
+      <c r="F67" s="46"/>
       <c r="G67" s="2"/>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" s="2"/>
-      <c r="B68" s="29" t="s">
+      <c r="B68" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="C68" s="30"/>
-      <c r="D68" s="30"/>
-      <c r="E68" s="30"/>
-      <c r="F68" s="31"/>
+      <c r="C68" s="23"/>
+      <c r="D68" s="23"/>
+      <c r="E68" s="23"/>
+      <c r="F68" s="24"/>
       <c r="G68" s="2"/>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" s="2"/>
-      <c r="B69" s="32"/>
-      <c r="C69" s="33"/>
-      <c r="D69" s="33"/>
-      <c r="E69" s="33"/>
-      <c r="F69" s="34"/>
+      <c r="B69" s="25"/>
+      <c r="C69" s="26"/>
+      <c r="D69" s="26"/>
+      <c r="E69" s="26"/>
+      <c r="F69" s="27"/>
       <c r="G69" s="2"/>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" s="2"/>
-      <c r="B70" s="35"/>
-      <c r="C70" s="36"/>
-      <c r="D70" s="36"/>
-      <c r="E70" s="36"/>
-      <c r="F70" s="37"/>
+      <c r="B70" s="28"/>
+      <c r="C70" s="29"/>
+      <c r="D70" s="29"/>
+      <c r="E70" s="29"/>
+      <c r="F70" s="30"/>
       <c r="G70" s="2"/>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
@@ -1924,29 +1942,29 @@
       <c r="G71" s="2"/>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A73" s="38" t="s">
-        <v>44</v>
-      </c>
-      <c r="B73" s="39"/>
-      <c r="C73" s="39"/>
-      <c r="D73" s="39"/>
-      <c r="E73" s="39"/>
-      <c r="F73" s="39"/>
-      <c r="G73" s="39"/>
+      <c r="A73" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="B73" s="21"/>
+      <c r="C73" s="21"/>
+      <c r="D73" s="21"/>
+      <c r="E73" s="21"/>
+      <c r="F73" s="21"/>
+      <c r="G73" s="21"/>
     </row>
     <row r="75" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="C75" s="50" t="s">
-        <v>54</v>
-      </c>
-      <c r="D75" s="50"/>
-      <c r="E75" s="50"/>
-      <c r="F75" s="50"/>
+        <v>39</v>
+      </c>
+      <c r="C75" s="34" t="s">
+        <v>43</v>
+      </c>
+      <c r="D75" s="34"/>
+      <c r="E75" s="34"/>
+      <c r="F75" s="34"/>
       <c r="G75" s="2"/>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
@@ -1963,12 +1981,12 @@
       <c r="B77" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="C77" s="51" t="s">
+      <c r="C77" s="35" t="s">
         <v>23</v>
       </c>
-      <c r="D77" s="51"/>
-      <c r="E77" s="51"/>
-      <c r="F77" s="52"/>
+      <c r="D77" s="35"/>
+      <c r="E77" s="35"/>
+      <c r="F77" s="36"/>
       <c r="G77" s="2"/>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
@@ -1976,12 +1994,12 @@
       <c r="B78" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C78" s="40" t="s">
-        <v>31</v>
-      </c>
-      <c r="D78" s="40"/>
-      <c r="E78" s="40"/>
-      <c r="F78" s="40"/>
+      <c r="C78" s="37" t="s">
+        <v>90</v>
+      </c>
+      <c r="D78" s="37"/>
+      <c r="E78" s="37"/>
+      <c r="F78" s="37"/>
       <c r="G78" s="2"/>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
@@ -1989,10 +2007,10 @@
       <c r="B79" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="C79" s="40"/>
-      <c r="D79" s="40"/>
-      <c r="E79" s="40"/>
-      <c r="F79" s="40"/>
+      <c r="C79" s="37"/>
+      <c r="D79" s="37"/>
+      <c r="E79" s="37"/>
+      <c r="F79" s="37"/>
       <c r="G79" s="2"/>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
@@ -2000,23 +2018,23 @@
       <c r="B80" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C80" s="40" t="s">
-        <v>51</v>
-      </c>
-      <c r="D80" s="40"/>
-      <c r="E80" s="40"/>
-      <c r="F80" s="40"/>
+      <c r="C80" s="37" t="s">
+        <v>91</v>
+      </c>
+      <c r="D80" s="37"/>
+      <c r="E80" s="37"/>
+      <c r="F80" s="37"/>
       <c r="G80" s="2"/>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" s="2"/>
-      <c r="B81" s="41" t="s">
+      <c r="B81" s="31" t="s">
         <v>7</v>
       </c>
-      <c r="C81" s="42"/>
-      <c r="D81" s="42"/>
-      <c r="E81" s="42"/>
-      <c r="F81" s="43"/>
+      <c r="C81" s="32"/>
+      <c r="D81" s="32"/>
+      <c r="E81" s="32"/>
+      <c r="F81" s="33"/>
       <c r="G81" s="2"/>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
@@ -2044,11 +2062,11 @@
         <v>1</v>
       </c>
       <c r="C83" s="7" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="D83" s="5"/>
       <c r="E83" s="7" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="F83" s="5" t="s">
         <v>13</v>
@@ -2061,11 +2079,11 @@
         <v>2</v>
       </c>
       <c r="C84" s="9" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="D84" s="9"/>
       <c r="E84" s="9" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="F84" s="8" t="s">
         <v>13</v>
@@ -2078,11 +2096,11 @@
         <v>3</v>
       </c>
       <c r="C85" s="9" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="D85" s="9"/>
       <c r="E85" s="9" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="F85" s="8" t="s">
         <v>13</v>
@@ -2091,11 +2109,11 @@
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" s="2"/>
-      <c r="B86" s="44"/>
-      <c r="C86" s="45"/>
-      <c r="D86" s="45"/>
-      <c r="E86" s="45"/>
-      <c r="F86" s="46"/>
+      <c r="B86" s="50"/>
+      <c r="C86" s="51"/>
+      <c r="D86" s="51"/>
+      <c r="E86" s="51"/>
+      <c r="F86" s="52"/>
       <c r="G86" s="2"/>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
@@ -2126,64 +2144,64 @@
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89" s="2"/>
-      <c r="B89" s="20" t="s">
+      <c r="B89" s="38" t="s">
         <v>18</v>
       </c>
-      <c r="C89" s="21"/>
-      <c r="D89" s="21"/>
-      <c r="E89" s="21"/>
-      <c r="F89" s="22"/>
+      <c r="C89" s="39"/>
+      <c r="D89" s="39"/>
+      <c r="E89" s="39"/>
+      <c r="F89" s="40"/>
       <c r="G89" s="2"/>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90" s="2"/>
-      <c r="B90" s="23" t="s">
+      <c r="B90" s="41" t="s">
         <v>19</v>
       </c>
-      <c r="C90" s="24"/>
-      <c r="D90" s="24"/>
-      <c r="E90" s="24"/>
-      <c r="F90" s="25"/>
+      <c r="C90" s="42"/>
+      <c r="D90" s="42"/>
+      <c r="E90" s="42"/>
+      <c r="F90" s="43"/>
       <c r="G90" s="2"/>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91" s="2"/>
-      <c r="B91" s="26" t="s">
+      <c r="B91" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="C91" s="27"/>
-      <c r="D91" s="27"/>
-      <c r="E91" s="27"/>
-      <c r="F91" s="28"/>
+      <c r="C91" s="45"/>
+      <c r="D91" s="45"/>
+      <c r="E91" s="45"/>
+      <c r="F91" s="46"/>
       <c r="G91" s="2"/>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92" s="2"/>
-      <c r="B92" s="29" t="s">
+      <c r="B92" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="C92" s="30"/>
-      <c r="D92" s="30"/>
-      <c r="E92" s="30"/>
-      <c r="F92" s="31"/>
+      <c r="C92" s="23"/>
+      <c r="D92" s="23"/>
+      <c r="E92" s="23"/>
+      <c r="F92" s="24"/>
       <c r="G92" s="2"/>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93" s="2"/>
-      <c r="B93" s="32"/>
-      <c r="C93" s="33"/>
-      <c r="D93" s="33"/>
-      <c r="E93" s="33"/>
-      <c r="F93" s="34"/>
+      <c r="B93" s="25"/>
+      <c r="C93" s="26"/>
+      <c r="D93" s="26"/>
+      <c r="E93" s="26"/>
+      <c r="F93" s="27"/>
       <c r="G93" s="2"/>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" s="2"/>
-      <c r="B94" s="35"/>
-      <c r="C94" s="36"/>
-      <c r="D94" s="36"/>
-      <c r="E94" s="36"/>
-      <c r="F94" s="37"/>
+      <c r="B94" s="28"/>
+      <c r="C94" s="29"/>
+      <c r="D94" s="29"/>
+      <c r="E94" s="29"/>
+      <c r="F94" s="30"/>
       <c r="G94" s="2"/>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
@@ -2191,29 +2209,29 @@
       <c r="G95" s="2"/>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A97" s="38" t="s">
-        <v>44</v>
-      </c>
-      <c r="B97" s="39"/>
-      <c r="C97" s="39"/>
-      <c r="D97" s="39"/>
-      <c r="E97" s="39"/>
-      <c r="F97" s="39"/>
-      <c r="G97" s="39"/>
+      <c r="A97" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="B97" s="21"/>
+      <c r="C97" s="21"/>
+      <c r="D97" s="21"/>
+      <c r="E97" s="21"/>
+      <c r="F97" s="21"/>
+      <c r="G97" s="21"/>
     </row>
     <row r="99" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="C99" s="50" t="s">
-        <v>61</v>
-      </c>
-      <c r="D99" s="50"/>
-      <c r="E99" s="50"/>
-      <c r="F99" s="50"/>
+        <v>42</v>
+      </c>
+      <c r="C99" s="34" t="s">
+        <v>50</v>
+      </c>
+      <c r="D99" s="34"/>
+      <c r="E99" s="34"/>
+      <c r="F99" s="34"/>
       <c r="G99" s="2"/>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
@@ -2230,12 +2248,12 @@
       <c r="B101" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="C101" s="51" t="s">
+      <c r="C101" s="35" t="s">
         <v>23</v>
       </c>
-      <c r="D101" s="51"/>
-      <c r="E101" s="51"/>
-      <c r="F101" s="52"/>
+      <c r="D101" s="35"/>
+      <c r="E101" s="35"/>
+      <c r="F101" s="36"/>
       <c r="G101" s="2"/>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
@@ -2243,12 +2261,12 @@
       <c r="B102" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C102" s="40" t="s">
-        <v>31</v>
-      </c>
-      <c r="D102" s="40"/>
-      <c r="E102" s="40"/>
-      <c r="F102" s="40"/>
+      <c r="C102" s="37" t="s">
+        <v>30</v>
+      </c>
+      <c r="D102" s="37"/>
+      <c r="E102" s="37"/>
+      <c r="F102" s="37"/>
       <c r="G102" s="2"/>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
@@ -2256,10 +2274,10 @@
       <c r="B103" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="C103" s="40"/>
-      <c r="D103" s="40"/>
-      <c r="E103" s="40"/>
-      <c r="F103" s="40"/>
+      <c r="C103" s="37"/>
+      <c r="D103" s="37"/>
+      <c r="E103" s="37"/>
+      <c r="F103" s="37"/>
       <c r="G103" s="2"/>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
@@ -2267,23 +2285,23 @@
       <c r="B104" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C104" s="40" t="s">
-        <v>51</v>
-      </c>
-      <c r="D104" s="40"/>
-      <c r="E104" s="40"/>
-      <c r="F104" s="40"/>
+      <c r="C104" s="37" t="s">
+        <v>40</v>
+      </c>
+      <c r="D104" s="37"/>
+      <c r="E104" s="37"/>
+      <c r="F104" s="37"/>
       <c r="G104" s="2"/>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105" s="2"/>
-      <c r="B105" s="41" t="s">
+      <c r="B105" s="31" t="s">
         <v>7</v>
       </c>
-      <c r="C105" s="42"/>
-      <c r="D105" s="42"/>
-      <c r="E105" s="42"/>
-      <c r="F105" s="43"/>
+      <c r="C105" s="32"/>
+      <c r="D105" s="32"/>
+      <c r="E105" s="32"/>
+      <c r="F105" s="33"/>
       <c r="G105" s="2"/>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
@@ -2311,13 +2329,13 @@
         <v>1</v>
       </c>
       <c r="C107" s="7" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="D107" s="7" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="E107" s="7" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="F107" s="5" t="s">
         <v>13</v>
@@ -2330,11 +2348,11 @@
         <v>2</v>
       </c>
       <c r="C108" s="9" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="D108" s="9"/>
       <c r="E108" s="9" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="F108" s="8" t="s">
         <v>13</v>
@@ -2347,11 +2365,11 @@
         <v>3</v>
       </c>
       <c r="C109" s="9" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="D109" s="9"/>
       <c r="E109" s="9" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="F109" s="8" t="s">
         <v>13</v>
@@ -2360,11 +2378,11 @@
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A110" s="2"/>
-      <c r="B110" s="44"/>
-      <c r="C110" s="45"/>
-      <c r="D110" s="45"/>
-      <c r="E110" s="45"/>
-      <c r="F110" s="46"/>
+      <c r="B110" s="50"/>
+      <c r="C110" s="51"/>
+      <c r="D110" s="51"/>
+      <c r="E110" s="51"/>
+      <c r="F110" s="52"/>
       <c r="G110" s="2"/>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
@@ -2395,64 +2413,64 @@
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A113" s="2"/>
-      <c r="B113" s="20" t="s">
+      <c r="B113" s="38" t="s">
         <v>18</v>
       </c>
-      <c r="C113" s="21"/>
-      <c r="D113" s="21"/>
-      <c r="E113" s="21"/>
-      <c r="F113" s="22"/>
+      <c r="C113" s="39"/>
+      <c r="D113" s="39"/>
+      <c r="E113" s="39"/>
+      <c r="F113" s="40"/>
       <c r="G113" s="2"/>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A114" s="2"/>
-      <c r="B114" s="23" t="s">
+      <c r="B114" s="41" t="s">
         <v>19</v>
       </c>
-      <c r="C114" s="24"/>
-      <c r="D114" s="24"/>
-      <c r="E114" s="24"/>
-      <c r="F114" s="25"/>
+      <c r="C114" s="42"/>
+      <c r="D114" s="42"/>
+      <c r="E114" s="42"/>
+      <c r="F114" s="43"/>
       <c r="G114" s="2"/>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A115" s="2"/>
-      <c r="B115" s="26" t="s">
+      <c r="B115" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="C115" s="27"/>
-      <c r="D115" s="27"/>
-      <c r="E115" s="27"/>
-      <c r="F115" s="28"/>
+      <c r="C115" s="45"/>
+      <c r="D115" s="45"/>
+      <c r="E115" s="45"/>
+      <c r="F115" s="46"/>
       <c r="G115" s="2"/>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A116" s="2"/>
-      <c r="B116" s="29" t="s">
+      <c r="B116" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="C116" s="30"/>
-      <c r="D116" s="30"/>
-      <c r="E116" s="30"/>
-      <c r="F116" s="31"/>
+      <c r="C116" s="23"/>
+      <c r="D116" s="23"/>
+      <c r="E116" s="23"/>
+      <c r="F116" s="24"/>
       <c r="G116" s="2"/>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A117" s="2"/>
-      <c r="B117" s="32"/>
-      <c r="C117" s="33"/>
-      <c r="D117" s="33"/>
-      <c r="E117" s="33"/>
-      <c r="F117" s="34"/>
+      <c r="B117" s="25"/>
+      <c r="C117" s="26"/>
+      <c r="D117" s="26"/>
+      <c r="E117" s="26"/>
+      <c r="F117" s="27"/>
       <c r="G117" s="2"/>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A118" s="2"/>
-      <c r="B118" s="35"/>
-      <c r="C118" s="36"/>
-      <c r="D118" s="36"/>
-      <c r="E118" s="36"/>
-      <c r="F118" s="37"/>
+      <c r="B118" s="28"/>
+      <c r="C118" s="29"/>
+      <c r="D118" s="29"/>
+      <c r="E118" s="29"/>
+      <c r="F118" s="30"/>
       <c r="G118" s="2"/>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
@@ -2460,29 +2478,29 @@
       <c r="G119" s="2"/>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A121" s="38" t="s">
-        <v>44</v>
-      </c>
-      <c r="B121" s="39"/>
-      <c r="C121" s="39"/>
-      <c r="D121" s="39"/>
-      <c r="E121" s="39"/>
-      <c r="F121" s="39"/>
-      <c r="G121" s="39"/>
+      <c r="A121" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="B121" s="21"/>
+      <c r="C121" s="21"/>
+      <c r="D121" s="21"/>
+      <c r="E121" s="21"/>
+      <c r="F121" s="21"/>
+      <c r="G121" s="21"/>
     </row>
     <row r="123" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B123" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="C123" s="50" t="s">
-        <v>70</v>
-      </c>
-      <c r="D123" s="50"/>
-      <c r="E123" s="50"/>
-      <c r="F123" s="50"/>
+        <v>49</v>
+      </c>
+      <c r="C123" s="34" t="s">
+        <v>59</v>
+      </c>
+      <c r="D123" s="34"/>
+      <c r="E123" s="34"/>
+      <c r="F123" s="34"/>
       <c r="G123" s="2"/>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.25">
@@ -2499,12 +2517,12 @@
       <c r="B125" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="C125" s="51" t="s">
+      <c r="C125" s="35" t="s">
         <v>23</v>
       </c>
-      <c r="D125" s="51"/>
-      <c r="E125" s="51"/>
-      <c r="F125" s="52"/>
+      <c r="D125" s="35"/>
+      <c r="E125" s="35"/>
+      <c r="F125" s="36"/>
       <c r="G125" s="2"/>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.25">
@@ -2512,12 +2530,12 @@
       <c r="B126" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C126" s="40" t="s">
-        <v>31</v>
-      </c>
-      <c r="D126" s="40"/>
-      <c r="E126" s="40"/>
-      <c r="F126" s="40"/>
+      <c r="C126" s="37" t="s">
+        <v>30</v>
+      </c>
+      <c r="D126" s="37"/>
+      <c r="E126" s="37"/>
+      <c r="F126" s="37"/>
       <c r="G126" s="2"/>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.25">
@@ -2525,10 +2543,10 @@
       <c r="B127" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="C127" s="40"/>
-      <c r="D127" s="40"/>
-      <c r="E127" s="40"/>
-      <c r="F127" s="40"/>
+      <c r="C127" s="37"/>
+      <c r="D127" s="37"/>
+      <c r="E127" s="37"/>
+      <c r="F127" s="37"/>
       <c r="G127" s="2"/>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.25">
@@ -2536,23 +2554,23 @@
       <c r="B128" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C128" s="40" t="s">
-        <v>85</v>
-      </c>
-      <c r="D128" s="40"/>
-      <c r="E128" s="40"/>
-      <c r="F128" s="40"/>
+      <c r="C128" s="37" t="s">
+        <v>74</v>
+      </c>
+      <c r="D128" s="37"/>
+      <c r="E128" s="37"/>
+      <c r="F128" s="37"/>
       <c r="G128" s="2"/>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A129" s="2"/>
-      <c r="B129" s="41" t="s">
+      <c r="B129" s="31" t="s">
         <v>7</v>
       </c>
-      <c r="C129" s="42"/>
-      <c r="D129" s="42"/>
-      <c r="E129" s="42"/>
-      <c r="F129" s="43"/>
+      <c r="C129" s="32"/>
+      <c r="D129" s="32"/>
+      <c r="E129" s="32"/>
+      <c r="F129" s="33"/>
       <c r="G129" s="2"/>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.25">
@@ -2580,11 +2598,11 @@
         <v>1</v>
       </c>
       <c r="C131" s="7" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="D131" s="7"/>
       <c r="E131" s="7" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="F131" s="5" t="s">
         <v>13</v>
@@ -2597,13 +2615,13 @@
         <v>2</v>
       </c>
       <c r="C132" s="9" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="D132" s="9" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="E132" s="9" t="s">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="F132" s="8" t="s">
         <v>13</v>
@@ -2616,11 +2634,11 @@
         <v>3</v>
       </c>
       <c r="C133" s="9" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="D133" s="9"/>
       <c r="E133" s="9" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="F133" s="8" t="s">
         <v>13</v>
@@ -2629,11 +2647,11 @@
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A134" s="2"/>
-      <c r="B134" s="44"/>
-      <c r="C134" s="45"/>
-      <c r="D134" s="45"/>
-      <c r="E134" s="45"/>
-      <c r="F134" s="46"/>
+      <c r="B134" s="50"/>
+      <c r="C134" s="51"/>
+      <c r="D134" s="51"/>
+      <c r="E134" s="51"/>
+      <c r="F134" s="52"/>
       <c r="G134" s="2"/>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.25">
@@ -2664,64 +2682,64 @@
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A137" s="2"/>
-      <c r="B137" s="20" t="s">
+      <c r="B137" s="38" t="s">
         <v>18</v>
       </c>
-      <c r="C137" s="21"/>
-      <c r="D137" s="21"/>
-      <c r="E137" s="21"/>
-      <c r="F137" s="22"/>
+      <c r="C137" s="39"/>
+      <c r="D137" s="39"/>
+      <c r="E137" s="39"/>
+      <c r="F137" s="40"/>
       <c r="G137" s="2"/>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A138" s="2"/>
-      <c r="B138" s="23" t="s">
+      <c r="B138" s="41" t="s">
         <v>19</v>
       </c>
-      <c r="C138" s="24"/>
-      <c r="D138" s="24"/>
-      <c r="E138" s="24"/>
-      <c r="F138" s="25"/>
+      <c r="C138" s="42"/>
+      <c r="D138" s="42"/>
+      <c r="E138" s="42"/>
+      <c r="F138" s="43"/>
       <c r="G138" s="2"/>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A139" s="2"/>
-      <c r="B139" s="26" t="s">
+      <c r="B139" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="C139" s="27"/>
-      <c r="D139" s="27"/>
-      <c r="E139" s="27"/>
-      <c r="F139" s="28"/>
+      <c r="C139" s="45"/>
+      <c r="D139" s="45"/>
+      <c r="E139" s="45"/>
+      <c r="F139" s="46"/>
       <c r="G139" s="2"/>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A140" s="2"/>
-      <c r="B140" s="29" t="s">
+      <c r="B140" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="C140" s="30"/>
-      <c r="D140" s="30"/>
-      <c r="E140" s="30"/>
-      <c r="F140" s="31"/>
+      <c r="C140" s="23"/>
+      <c r="D140" s="23"/>
+      <c r="E140" s="23"/>
+      <c r="F140" s="24"/>
       <c r="G140" s="2"/>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A141" s="2"/>
-      <c r="B141" s="32"/>
-      <c r="C141" s="33"/>
-      <c r="D141" s="33"/>
-      <c r="E141" s="33"/>
-      <c r="F141" s="34"/>
+      <c r="B141" s="25"/>
+      <c r="C141" s="26"/>
+      <c r="D141" s="26"/>
+      <c r="E141" s="26"/>
+      <c r="F141" s="27"/>
       <c r="G141" s="2"/>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A142" s="2"/>
-      <c r="B142" s="35"/>
-      <c r="C142" s="36"/>
-      <c r="D142" s="36"/>
-      <c r="E142" s="36"/>
-      <c r="F142" s="37"/>
+      <c r="B142" s="28"/>
+      <c r="C142" s="29"/>
+      <c r="D142" s="29"/>
+      <c r="E142" s="29"/>
+      <c r="F142" s="30"/>
       <c r="G142" s="2"/>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.25">
@@ -2729,29 +2747,29 @@
       <c r="G143" s="2"/>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A145" s="38" t="s">
-        <v>44</v>
-      </c>
-      <c r="B145" s="39"/>
-      <c r="C145" s="39"/>
-      <c r="D145" s="39"/>
-      <c r="E145" s="39"/>
-      <c r="F145" s="39"/>
-      <c r="G145" s="39"/>
+      <c r="A145" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="B145" s="21"/>
+      <c r="C145" s="21"/>
+      <c r="D145" s="21"/>
+      <c r="E145" s="21"/>
+      <c r="F145" s="21"/>
+      <c r="G145" s="21"/>
     </row>
     <row r="147" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B147" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="C147" s="50" t="s">
-        <v>78</v>
-      </c>
-      <c r="D147" s="50"/>
-      <c r="E147" s="50"/>
-      <c r="F147" s="50"/>
+        <v>58</v>
+      </c>
+      <c r="C147" s="34" t="s">
+        <v>67</v>
+      </c>
+      <c r="D147" s="34"/>
+      <c r="E147" s="34"/>
+      <c r="F147" s="34"/>
       <c r="G147" s="2"/>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.25">
@@ -2768,12 +2786,12 @@
       <c r="B149" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="C149" s="51" t="s">
+      <c r="C149" s="35" t="s">
         <v>23</v>
       </c>
-      <c r="D149" s="51"/>
-      <c r="E149" s="51"/>
-      <c r="F149" s="52"/>
+      <c r="D149" s="35"/>
+      <c r="E149" s="35"/>
+      <c r="F149" s="36"/>
       <c r="G149" s="2"/>
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.25">
@@ -2781,12 +2799,12 @@
       <c r="B150" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C150" s="40" t="s">
-        <v>31</v>
-      </c>
-      <c r="D150" s="40"/>
-      <c r="E150" s="40"/>
-      <c r="F150" s="40"/>
+      <c r="C150" s="37" t="s">
+        <v>30</v>
+      </c>
+      <c r="D150" s="37"/>
+      <c r="E150" s="37"/>
+      <c r="F150" s="37"/>
       <c r="G150" s="2"/>
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.25">
@@ -2794,10 +2812,10 @@
       <c r="B151" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="C151" s="40"/>
-      <c r="D151" s="40"/>
-      <c r="E151" s="40"/>
-      <c r="F151" s="40"/>
+      <c r="C151" s="37"/>
+      <c r="D151" s="37"/>
+      <c r="E151" s="37"/>
+      <c r="F151" s="37"/>
       <c r="G151" s="2"/>
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.25">
@@ -2805,23 +2823,23 @@
       <c r="B152" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C152" s="40" t="s">
-        <v>85</v>
-      </c>
-      <c r="D152" s="40"/>
-      <c r="E152" s="40"/>
-      <c r="F152" s="40"/>
+      <c r="C152" s="37" t="s">
+        <v>74</v>
+      </c>
+      <c r="D152" s="37"/>
+      <c r="E152" s="37"/>
+      <c r="F152" s="37"/>
       <c r="G152" s="2"/>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A153" s="2"/>
-      <c r="B153" s="41" t="s">
+      <c r="B153" s="31" t="s">
         <v>7</v>
       </c>
-      <c r="C153" s="42"/>
-      <c r="D153" s="42"/>
-      <c r="E153" s="42"/>
-      <c r="F153" s="43"/>
+      <c r="C153" s="32"/>
+      <c r="D153" s="32"/>
+      <c r="E153" s="32"/>
+      <c r="F153" s="33"/>
       <c r="G153" s="2"/>
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.25">
@@ -2849,11 +2867,11 @@
         <v>1</v>
       </c>
       <c r="C155" s="7" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="D155" s="7"/>
       <c r="E155" s="7" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="F155" s="5" t="s">
         <v>13</v>
@@ -2866,13 +2884,13 @@
         <v>2</v>
       </c>
       <c r="C156" s="9" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="D156" s="9" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="E156" s="9" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="F156" s="8" t="s">
         <v>13</v>
@@ -2885,13 +2903,13 @@
         <v>3</v>
       </c>
       <c r="C157" s="9" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="D157" s="9" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="E157" s="9" t="s">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="F157" s="8" t="s">
         <v>13</v>
@@ -2904,11 +2922,11 @@
         <v>4</v>
       </c>
       <c r="C158" s="9" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="D158" s="9"/>
       <c r="E158" s="9" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="F158" s="8" t="s">
         <v>13</v>
@@ -2917,11 +2935,11 @@
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A159" s="2"/>
-      <c r="B159" s="44"/>
-      <c r="C159" s="45"/>
-      <c r="D159" s="45"/>
-      <c r="E159" s="45"/>
-      <c r="F159" s="46"/>
+      <c r="B159" s="50"/>
+      <c r="C159" s="51"/>
+      <c r="D159" s="51"/>
+      <c r="E159" s="51"/>
+      <c r="F159" s="52"/>
       <c r="G159" s="2"/>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.25">
@@ -2952,64 +2970,64 @@
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A162" s="2"/>
-      <c r="B162" s="20" t="s">
+      <c r="B162" s="38" t="s">
         <v>18</v>
       </c>
-      <c r="C162" s="21"/>
-      <c r="D162" s="21"/>
-      <c r="E162" s="21"/>
-      <c r="F162" s="22"/>
+      <c r="C162" s="39"/>
+      <c r="D162" s="39"/>
+      <c r="E162" s="39"/>
+      <c r="F162" s="40"/>
       <c r="G162" s="2"/>
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A163" s="2"/>
-      <c r="B163" s="23" t="s">
+      <c r="B163" s="41" t="s">
         <v>19</v>
       </c>
-      <c r="C163" s="24"/>
-      <c r="D163" s="24"/>
-      <c r="E163" s="24"/>
-      <c r="F163" s="25"/>
+      <c r="C163" s="42"/>
+      <c r="D163" s="42"/>
+      <c r="E163" s="42"/>
+      <c r="F163" s="43"/>
       <c r="G163" s="2"/>
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A164" s="2"/>
-      <c r="B164" s="26" t="s">
+      <c r="B164" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="C164" s="27"/>
-      <c r="D164" s="27"/>
-      <c r="E164" s="27"/>
-      <c r="F164" s="28"/>
+      <c r="C164" s="45"/>
+      <c r="D164" s="45"/>
+      <c r="E164" s="45"/>
+      <c r="F164" s="46"/>
       <c r="G164" s="2"/>
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A165" s="2"/>
-      <c r="B165" s="29" t="s">
+      <c r="B165" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="C165" s="30"/>
-      <c r="D165" s="30"/>
-      <c r="E165" s="30"/>
-      <c r="F165" s="31"/>
+      <c r="C165" s="23"/>
+      <c r="D165" s="23"/>
+      <c r="E165" s="23"/>
+      <c r="F165" s="24"/>
       <c r="G165" s="2"/>
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A166" s="2"/>
-      <c r="B166" s="32"/>
-      <c r="C166" s="33"/>
-      <c r="D166" s="33"/>
-      <c r="E166" s="33"/>
-      <c r="F166" s="34"/>
+      <c r="B166" s="25"/>
+      <c r="C166" s="26"/>
+      <c r="D166" s="26"/>
+      <c r="E166" s="26"/>
+      <c r="F166" s="27"/>
       <c r="G166" s="2"/>
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A167" s="2"/>
-      <c r="B167" s="35"/>
-      <c r="C167" s="36"/>
-      <c r="D167" s="36"/>
-      <c r="E167" s="36"/>
-      <c r="F167" s="37"/>
+      <c r="B167" s="28"/>
+      <c r="C167" s="29"/>
+      <c r="D167" s="29"/>
+      <c r="E167" s="29"/>
+      <c r="F167" s="30"/>
       <c r="G167" s="2"/>
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.25">
@@ -3017,38 +3035,75 @@
       <c r="G168" s="2"/>
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A170" s="38" t="s">
-        <v>44</v>
-      </c>
-      <c r="B170" s="39"/>
-      <c r="C170" s="39"/>
-      <c r="D170" s="39"/>
-      <c r="E170" s="39"/>
-      <c r="F170" s="39"/>
-      <c r="G170" s="39"/>
+      <c r="A170" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="B170" s="21"/>
+      <c r="C170" s="21"/>
+      <c r="D170" s="21"/>
+      <c r="E170" s="21"/>
+      <c r="F170" s="21"/>
+      <c r="G170" s="21"/>
     </row>
   </sheetData>
   <mergeCells count="93">
-    <mergeCell ref="A73:G73"/>
-    <mergeCell ref="B68:F70"/>
-    <mergeCell ref="B58:F58"/>
-    <mergeCell ref="C52:F52"/>
-    <mergeCell ref="C54:F54"/>
-    <mergeCell ref="C55:F55"/>
-    <mergeCell ref="C56:F56"/>
-    <mergeCell ref="C57:F57"/>
-    <mergeCell ref="B65:F65"/>
-    <mergeCell ref="B66:F66"/>
-    <mergeCell ref="B67:F67"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B62:F62"/>
-    <mergeCell ref="B11:F11"/>
-    <mergeCell ref="C1:E1"/>
-    <mergeCell ref="C3:E3"/>
-    <mergeCell ref="C7:F7"/>
-    <mergeCell ref="C8:F8"/>
-    <mergeCell ref="C9:F9"/>
-    <mergeCell ref="C10:F10"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B163:F163"/>
+    <mergeCell ref="B164:F164"/>
+    <mergeCell ref="B165:F167"/>
+    <mergeCell ref="A170:G170"/>
+    <mergeCell ref="C151:F151"/>
+    <mergeCell ref="C152:F152"/>
+    <mergeCell ref="B153:F153"/>
+    <mergeCell ref="B159:F159"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B140:F142"/>
+    <mergeCell ref="A145:G145"/>
+    <mergeCell ref="C147:F147"/>
+    <mergeCell ref="C149:F149"/>
+    <mergeCell ref="C150:F150"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B136:F136"/>
+    <mergeCell ref="B137:F137"/>
+    <mergeCell ref="B138:F138"/>
+    <mergeCell ref="B139:F139"/>
+    <mergeCell ref="C125:F125"/>
+    <mergeCell ref="C126:F126"/>
+    <mergeCell ref="C127:F127"/>
+    <mergeCell ref="C128:F128"/>
+    <mergeCell ref="B129:F129"/>
+    <mergeCell ref="C123:F123"/>
+    <mergeCell ref="A97:G97"/>
+    <mergeCell ref="C75:F75"/>
+    <mergeCell ref="C79:F79"/>
+    <mergeCell ref="C80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B88:F88"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B90:F90"/>
+    <mergeCell ref="B91:F91"/>
+    <mergeCell ref="B92:F94"/>
+    <mergeCell ref="B86:F86"/>
+    <mergeCell ref="C77:F77"/>
+    <mergeCell ref="C78:F78"/>
+    <mergeCell ref="B115:F115"/>
+    <mergeCell ref="B116:F118"/>
+    <mergeCell ref="A121:G121"/>
+    <mergeCell ref="B105:F105"/>
+    <mergeCell ref="B110:F110"/>
+    <mergeCell ref="B112:F112"/>
+    <mergeCell ref="B113:F113"/>
+    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="C99:F99"/>
+    <mergeCell ref="C101:F101"/>
+    <mergeCell ref="C102:F102"/>
+    <mergeCell ref="C103:F103"/>
+    <mergeCell ref="C104:F104"/>
+    <mergeCell ref="B44:F46"/>
+    <mergeCell ref="B41:F41"/>
+    <mergeCell ref="B42:F42"/>
+    <mergeCell ref="B43:F43"/>
+    <mergeCell ref="B40:F40"/>
     <mergeCell ref="C32:F32"/>
     <mergeCell ref="A49:G49"/>
     <mergeCell ref="B14:F14"/>
@@ -3065,63 +3120,26 @@
     <mergeCell ref="C29:F29"/>
     <mergeCell ref="C30:F30"/>
     <mergeCell ref="C31:F31"/>
-    <mergeCell ref="B44:F46"/>
-    <mergeCell ref="B41:F41"/>
-    <mergeCell ref="B42:F42"/>
-    <mergeCell ref="B43:F43"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="C99:F99"/>
-    <mergeCell ref="C101:F101"/>
-    <mergeCell ref="C102:F102"/>
-    <mergeCell ref="C103:F103"/>
-    <mergeCell ref="C104:F104"/>
-    <mergeCell ref="A121:G121"/>
-    <mergeCell ref="B105:F105"/>
-    <mergeCell ref="B110:F110"/>
-    <mergeCell ref="B112:F112"/>
-    <mergeCell ref="B113:F113"/>
-    <mergeCell ref="B114:F114"/>
-    <mergeCell ref="C123:F123"/>
-    <mergeCell ref="A97:G97"/>
-    <mergeCell ref="C75:F75"/>
-    <mergeCell ref="C79:F79"/>
-    <mergeCell ref="C80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B88:F88"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B90:F90"/>
-    <mergeCell ref="B91:F91"/>
-    <mergeCell ref="B92:F94"/>
-    <mergeCell ref="B86:F86"/>
-    <mergeCell ref="C77:F77"/>
-    <mergeCell ref="C78:F78"/>
-    <mergeCell ref="B115:F115"/>
-    <mergeCell ref="B116:F118"/>
-    <mergeCell ref="C125:F125"/>
-    <mergeCell ref="C126:F126"/>
-    <mergeCell ref="C127:F127"/>
-    <mergeCell ref="C128:F128"/>
-    <mergeCell ref="B129:F129"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B136:F136"/>
-    <mergeCell ref="B137:F137"/>
-    <mergeCell ref="B138:F138"/>
-    <mergeCell ref="B139:F139"/>
-    <mergeCell ref="B140:F142"/>
-    <mergeCell ref="A145:G145"/>
-    <mergeCell ref="C147:F147"/>
-    <mergeCell ref="C149:F149"/>
-    <mergeCell ref="C150:F150"/>
-    <mergeCell ref="C151:F151"/>
-    <mergeCell ref="C152:F152"/>
-    <mergeCell ref="B153:F153"/>
-    <mergeCell ref="B159:F159"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B163:F163"/>
-    <mergeCell ref="B164:F164"/>
-    <mergeCell ref="B165:F167"/>
-    <mergeCell ref="A170:G170"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="C3:E3"/>
+    <mergeCell ref="C7:F7"/>
+    <mergeCell ref="C8:F8"/>
+    <mergeCell ref="C9:F9"/>
+    <mergeCell ref="C10:F10"/>
+    <mergeCell ref="A73:G73"/>
+    <mergeCell ref="B68:F70"/>
+    <mergeCell ref="B58:F58"/>
+    <mergeCell ref="C52:F52"/>
+    <mergeCell ref="C54:F54"/>
+    <mergeCell ref="C55:F55"/>
+    <mergeCell ref="C56:F56"/>
+    <mergeCell ref="C57:F57"/>
+    <mergeCell ref="B65:F65"/>
+    <mergeCell ref="B66:F66"/>
+    <mergeCell ref="B67:F67"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B62:F62"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
